--- a/research/traditional_assets/database/data/austria/austria_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_hotel_gaming.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08218179047585426</v>
+        <v>0.08201875417871221</v>
       </c>
       <c r="C2">
-        <v>190.6086187209954</v>
+        <v>188.9016531073995</v>
       </c>
       <c r="D2">
-        <v>189.1286187209954</v>
+        <v>189.4756531073996</v>
       </c>
       <c r="E2">
-        <v>-174.6</v>
+        <v>-172.546</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.054</v>
       </c>
       <c r="G2">
         <v>1.48</v>
@@ -1439,28 +1439,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1033162</v>
       </c>
       <c r="N2">
-        <v>36.08666666666667</v>
+        <v>35.98335046666666</v>
       </c>
       <c r="O2">
-        <v>8.6608</v>
+        <v>8.636004111999998</v>
       </c>
       <c r="P2">
-        <v>27.42586666666666</v>
+        <v>27.34734635466667</v>
       </c>
       <c r="Q2">
-        <v>30.00586666666666</v>
+        <v>29.92734635466667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08218179047585426</v>
+        <v>0.08246108502900223</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7537904946568498</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>349.2837199458232</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08201875417871221</v>
+        <v>0.08185571788157017</v>
       </c>
       <c r="C3">
-        <v>188.9016531073995</v>
+        <v>187.195963390134</v>
       </c>
       <c r="D3">
-        <v>189.4756531073996</v>
+        <v>189.823963390134</v>
       </c>
       <c r="E3">
-        <v>-172.546</v>
+        <v>-170.492</v>
       </c>
       <c r="F3">
-        <v>2.054</v>
+        <v>4.108000000000001</v>
       </c>
       <c r="G3">
         <v>1.48</v>
@@ -1521,28 +1521,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M3">
-        <v>0.1033162</v>
+        <v>0.2066324</v>
       </c>
       <c r="N3">
-        <v>35.98335046666666</v>
+        <v>35.88003426666667</v>
       </c>
       <c r="O3">
-        <v>8.636004111999998</v>
+        <v>8.611208224</v>
       </c>
       <c r="P3">
-        <v>27.34734635466667</v>
+        <v>27.26882604266667</v>
       </c>
       <c r="Q3">
-        <v>29.92734635466667</v>
+        <v>29.84882604266667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08246108502900223</v>
+        <v>0.08274607947098997</v>
       </c>
       <c r="T3">
-        <v>0.7537904946568498</v>
+        <v>0.7596502803459648</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>349.2837199458232</v>
+        <v>174.6418599729116</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08185571788157017</v>
+        <v>0.08169268158442811</v>
       </c>
       <c r="C4">
-        <v>187.195963390134</v>
+        <v>185.4915566185415</v>
       </c>
       <c r="D4">
-        <v>189.823963390134</v>
+        <v>190.1735566185415</v>
       </c>
       <c r="E4">
-        <v>-170.492</v>
+        <v>-168.438</v>
       </c>
       <c r="F4">
-        <v>4.108000000000001</v>
+        <v>6.162</v>
       </c>
       <c r="G4">
         <v>1.48</v>
@@ -1603,28 +1603,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M4">
-        <v>0.2066324</v>
+        <v>0.3099486</v>
       </c>
       <c r="N4">
-        <v>35.88003426666667</v>
+        <v>35.77671806666667</v>
       </c>
       <c r="O4">
-        <v>8.611208224</v>
+        <v>8.586412336</v>
       </c>
       <c r="P4">
-        <v>27.26882604266667</v>
+        <v>27.19030573066667</v>
       </c>
       <c r="Q4">
-        <v>29.84882604266667</v>
+        <v>29.77030573066666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08274607947098997</v>
+        <v>0.08303695008703929</v>
       </c>
       <c r="T4">
-        <v>0.7596502803459648</v>
+        <v>0.765630886358567</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>174.6418599729116</v>
+        <v>116.4279066486078</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08169268158442811</v>
+        <v>0.08152964528728607</v>
       </c>
       <c r="C5">
-        <v>185.4915566185415</v>
+        <v>183.7884398939906</v>
       </c>
       <c r="D5">
-        <v>190.1735566185415</v>
+        <v>190.5244398939906</v>
       </c>
       <c r="E5">
-        <v>-168.438</v>
+        <v>-166.384</v>
       </c>
       <c r="F5">
-        <v>6.162</v>
+        <v>8.216000000000001</v>
       </c>
       <c r="G5">
         <v>1.48</v>
@@ -1685,28 +1685,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M5">
-        <v>0.3099486</v>
+        <v>0.4132648</v>
       </c>
       <c r="N5">
-        <v>35.77671806666667</v>
+        <v>35.67340186666667</v>
       </c>
       <c r="O5">
-        <v>8.586412336</v>
+        <v>8.561616447999999</v>
       </c>
       <c r="P5">
-        <v>27.19030573066667</v>
+        <v>27.11178541866667</v>
       </c>
       <c r="Q5">
-        <v>29.77030573066666</v>
+        <v>29.69178541866667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08303695008703929</v>
+        <v>0.08333388050758966</v>
       </c>
       <c r="T5">
-        <v>0.765630886358567</v>
+        <v>0.7717360883297649</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>116.4279066486078</v>
+        <v>87.32092998645581</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08152964528728607</v>
+        <v>0.08136660899014402</v>
       </c>
       <c r="C6">
-        <v>183.7884398939906</v>
+        <v>182.086620370357</v>
       </c>
       <c r="D6">
-        <v>190.5244398939906</v>
+        <v>190.876620370357</v>
       </c>
       <c r="E6">
-        <v>-166.384</v>
+        <v>-164.33</v>
       </c>
       <c r="F6">
-        <v>8.216000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="G6">
         <v>1.48</v>
@@ -1767,28 +1767,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M6">
-        <v>0.4132648</v>
+        <v>0.5165810000000001</v>
       </c>
       <c r="N6">
-        <v>35.67340186666667</v>
+        <v>35.57008566666666</v>
       </c>
       <c r="O6">
-        <v>8.561616447999999</v>
+        <v>8.536820559999999</v>
       </c>
       <c r="P6">
-        <v>27.11178541866667</v>
+        <v>27.03326510666666</v>
       </c>
       <c r="Q6">
-        <v>29.69178541866667</v>
+        <v>29.61326510666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08333388050758966</v>
+        <v>0.08363706209488844</v>
       </c>
       <c r="T6">
-        <v>0.7717360883297649</v>
+        <v>0.7779698208687775</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>87.32092998645581</v>
+        <v>69.85674398916464</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08136660899014402</v>
+        <v>0.08120357269300198</v>
       </c>
       <c r="C7">
-        <v>182.086620370357</v>
+        <v>180.3861052545094</v>
       </c>
       <c r="D7">
-        <v>190.876620370357</v>
+        <v>191.2301052545094</v>
       </c>
       <c r="E7">
-        <v>-164.33</v>
+        <v>-162.276</v>
       </c>
       <c r="F7">
-        <v>10.27</v>
+        <v>12.324</v>
       </c>
       <c r="G7">
         <v>1.48</v>
@@ -1849,28 +1849,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M7">
-        <v>0.5165810000000001</v>
+        <v>0.6198972</v>
       </c>
       <c r="N7">
-        <v>35.57008566666666</v>
+        <v>35.46676946666667</v>
       </c>
       <c r="O7">
-        <v>8.536820559999999</v>
+        <v>8.512024672000001</v>
       </c>
       <c r="P7">
-        <v>27.03326510666666</v>
+        <v>26.95474479466667</v>
       </c>
       <c r="Q7">
-        <v>29.61326510666667</v>
+        <v>29.53474479466666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08363706209488844</v>
+        <v>0.08394669435425742</v>
       </c>
       <c r="T7">
-        <v>0.7779698208687775</v>
+        <v>0.7843361860150032</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>69.85674398916464</v>
+        <v>58.21395332430388</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08120357269300198</v>
+        <v>0.08104053639585992</v>
       </c>
       <c r="C8">
-        <v>180.3861052545094</v>
+        <v>178.6869018068013</v>
       </c>
       <c r="D8">
-        <v>191.2301052545094</v>
+        <v>191.5849018068013</v>
       </c>
       <c r="E8">
-        <v>-162.276</v>
+        <v>-160.222</v>
       </c>
       <c r="F8">
-        <v>12.324</v>
+        <v>14.378</v>
       </c>
       <c r="G8">
         <v>1.48</v>
@@ -1931,28 +1931,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M8">
-        <v>0.6198971999999999</v>
+        <v>0.7232133999999999</v>
       </c>
       <c r="N8">
-        <v>35.46676946666667</v>
+        <v>35.36345326666667</v>
       </c>
       <c r="O8">
-        <v>8.512024672000001</v>
+        <v>8.487228783999999</v>
       </c>
       <c r="P8">
-        <v>26.95474479466667</v>
+        <v>26.87622448266667</v>
       </c>
       <c r="Q8">
-        <v>29.53474479466666</v>
+        <v>29.45622448266667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08394669435425742</v>
+        <v>0.08426298537189238</v>
       </c>
       <c r="T8">
-        <v>0.7843361860150032</v>
+        <v>0.7908394622396423</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>58.21395332430389</v>
+        <v>49.89767427797476</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08104053639585991</v>
+        <v>0.08087750009871787</v>
       </c>
       <c r="C9">
-        <v>178.6869018068013</v>
+        <v>176.9890173415679</v>
       </c>
       <c r="D9">
-        <v>191.5849018068013</v>
+        <v>191.9410173415679</v>
       </c>
       <c r="E9">
-        <v>-160.222</v>
+        <v>-158.168</v>
       </c>
       <c r="F9">
-        <v>14.378</v>
+        <v>16.432</v>
       </c>
       <c r="G9">
         <v>1.48</v>
@@ -2013,28 +2013,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M9">
-        <v>0.7232134</v>
+        <v>0.8265296000000001</v>
       </c>
       <c r="N9">
-        <v>35.36345326666667</v>
+        <v>35.26013706666667</v>
       </c>
       <c r="O9">
-        <v>8.487228783999999</v>
+        <v>8.462432895999999</v>
       </c>
       <c r="P9">
-        <v>26.87622448266667</v>
+        <v>26.79770417066667</v>
       </c>
       <c r="Q9">
-        <v>29.45622448266667</v>
+        <v>29.37770417066667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08426298537189238</v>
+        <v>0.08458615228121508</v>
       </c>
       <c r="T9">
-        <v>0.7908394622396423</v>
+        <v>0.7974841140343822</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>49.89767427797475</v>
+        <v>43.6604649932279</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08087750009871787</v>
+        <v>0.08071446380157581</v>
       </c>
       <c r="C10">
-        <v>176.9890173415679</v>
+        <v>175.2924592276289</v>
       </c>
       <c r="D10">
-        <v>191.9410173415679</v>
+        <v>192.2984592276289</v>
       </c>
       <c r="E10">
-        <v>-158.168</v>
+        <v>-156.114</v>
       </c>
       <c r="F10">
-        <v>16.432</v>
+        <v>18.486</v>
       </c>
       <c r="G10">
         <v>1.48</v>
@@ -2095,28 +2095,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M10">
-        <v>0.8265296000000001</v>
+        <v>0.9298457999999999</v>
       </c>
       <c r="N10">
-        <v>35.26013706666667</v>
+        <v>35.15682086666666</v>
       </c>
       <c r="O10">
-        <v>8.462432895999999</v>
+        <v>8.437637007999999</v>
       </c>
       <c r="P10">
-        <v>26.79770417066667</v>
+        <v>26.71918385866666</v>
       </c>
       <c r="Q10">
-        <v>29.37770417066667</v>
+        <v>29.29918385866667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08458615228121508</v>
+        <v>0.08491642175997341</v>
       </c>
       <c r="T10">
-        <v>0.7974841140343822</v>
+        <v>0.8042748021323033</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>43.6604649932279</v>
+        <v>38.80930221620258</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08071446380157581</v>
+        <v>0.08055142750443377</v>
       </c>
       <c r="C11">
-        <v>175.2924592276289</v>
+        <v>173.5972348887968</v>
       </c>
       <c r="D11">
-        <v>192.2984592276289</v>
+        <v>192.6572348887968</v>
       </c>
       <c r="E11">
-        <v>-156.114</v>
+        <v>-154.06</v>
       </c>
       <c r="F11">
-        <v>18.486</v>
+        <v>20.54</v>
       </c>
       <c r="G11">
         <v>1.48</v>
@@ -2177,28 +2177,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M11">
-        <v>0.9298457999999999</v>
+        <v>1.033162</v>
       </c>
       <c r="N11">
-        <v>35.15682086666666</v>
+        <v>35.05350466666667</v>
       </c>
       <c r="O11">
-        <v>8.437637007999999</v>
+        <v>8.41284112</v>
       </c>
       <c r="P11">
-        <v>26.71918385866666</v>
+        <v>26.64066354666667</v>
       </c>
       <c r="Q11">
-        <v>29.29918385866667</v>
+        <v>29.22066354666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08491642175997341</v>
+        <v>0.08525403056048196</v>
       </c>
       <c r="T11">
-        <v>0.8042748021323033</v>
+        <v>0.8112163944101783</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>38.80930221620258</v>
+        <v>34.92837199458233</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08055142750443377</v>
+        <v>0.08038839120729172</v>
       </c>
       <c r="C12">
-        <v>173.5972348887968</v>
+        <v>171.9033518043906</v>
       </c>
       <c r="D12">
-        <v>192.6572348887968</v>
+        <v>193.0173518043906</v>
       </c>
       <c r="E12">
-        <v>-154.06</v>
+        <v>-152.006</v>
       </c>
       <c r="F12">
-        <v>20.54</v>
+        <v>22.594</v>
       </c>
       <c r="G12">
         <v>1.48</v>
@@ -2259,28 +2259,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M12">
-        <v>1.033162</v>
+        <v>1.1364782</v>
       </c>
       <c r="N12">
-        <v>35.05350466666667</v>
+        <v>34.95018846666667</v>
       </c>
       <c r="O12">
-        <v>8.41284112</v>
+        <v>8.388045232</v>
       </c>
       <c r="P12">
-        <v>26.64066354666667</v>
+        <v>26.56214323466667</v>
       </c>
       <c r="Q12">
-        <v>29.22066354666667</v>
+        <v>29.14214323466667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08525403056048196</v>
+        <v>0.08559922607560867</v>
       </c>
       <c r="T12">
-        <v>0.8112163944101783</v>
+        <v>0.8183139775257583</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.92837199458233</v>
+        <v>31.7530654496203</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08038839120729172</v>
+        <v>0.08022535491014965</v>
       </c>
       <c r="C13">
-        <v>171.9033518043906</v>
+        <v>170.2108175097558</v>
       </c>
       <c r="D13">
-        <v>193.0173518043906</v>
+        <v>193.3788175097558</v>
       </c>
       <c r="E13">
-        <v>-152.006</v>
+        <v>-149.952</v>
       </c>
       <c r="F13">
-        <v>22.594</v>
+        <v>24.648</v>
       </c>
       <c r="G13">
         <v>1.48</v>
@@ -2341,28 +2341,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M13">
-        <v>1.1364782</v>
+        <v>1.2397944</v>
       </c>
       <c r="N13">
-        <v>34.95018846666667</v>
+        <v>34.84687226666667</v>
       </c>
       <c r="O13">
-        <v>8.388045232</v>
+        <v>8.363249344</v>
       </c>
       <c r="P13">
-        <v>26.56214323466667</v>
+        <v>26.48362292266667</v>
       </c>
       <c r="Q13">
-        <v>29.14214323466667</v>
+        <v>29.06362292266667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08559922607560867</v>
+        <v>0.08595226694335188</v>
       </c>
       <c r="T13">
-        <v>0.8183139775257583</v>
+        <v>0.8255728693485103</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.7530654496203</v>
+        <v>29.10697666215194</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08022535491014965</v>
+        <v>0.08006231861300761</v>
       </c>
       <c r="C14">
-        <v>170.2108175097558</v>
+        <v>168.5196395967899</v>
       </c>
       <c r="D14">
-        <v>193.3788175097558</v>
+        <v>193.7416395967899</v>
       </c>
       <c r="E14">
-        <v>-149.952</v>
+        <v>-147.898</v>
       </c>
       <c r="F14">
-        <v>24.648</v>
+        <v>26.702</v>
       </c>
       <c r="G14">
         <v>1.48</v>
@@ -2423,28 +2423,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M14">
-        <v>1.2397944</v>
+        <v>1.3431106</v>
       </c>
       <c r="N14">
-        <v>34.84687226666667</v>
+        <v>34.74355606666666</v>
       </c>
       <c r="O14">
-        <v>8.363249344</v>
+        <v>8.338453455999998</v>
       </c>
       <c r="P14">
-        <v>26.48362292266667</v>
+        <v>26.40510261066667</v>
       </c>
       <c r="Q14">
-        <v>29.06362292266667</v>
+        <v>28.98510261066667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08595226694335188</v>
+        <v>0.08631342369311221</v>
       </c>
       <c r="T14">
-        <v>0.8255728693485103</v>
+        <v>0.8329986322476477</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.10697666215194</v>
+        <v>26.86797845737102</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08006231861300761</v>
+        <v>0.07989928231586554</v>
       </c>
       <c r="C15">
-        <v>168.5196395967899</v>
+        <v>166.8298257144739</v>
       </c>
       <c r="D15">
-        <v>193.7416395967899</v>
+        <v>194.1058257144739</v>
       </c>
       <c r="E15">
-        <v>-147.898</v>
+        <v>-145.844</v>
       </c>
       <c r="F15">
-        <v>26.702</v>
+        <v>28.756</v>
       </c>
       <c r="G15">
         <v>1.48</v>
@@ -2505,28 +2505,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M15">
-        <v>1.3431106</v>
+        <v>1.4464268</v>
       </c>
       <c r="N15">
-        <v>34.74355606666666</v>
+        <v>34.64023986666667</v>
       </c>
       <c r="O15">
-        <v>8.338453455999998</v>
+        <v>8.313657568</v>
       </c>
       <c r="P15">
-        <v>26.40510261066667</v>
+        <v>26.32658229866667</v>
       </c>
       <c r="Q15">
-        <v>28.98510261066667</v>
+        <v>28.90658229866667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08631342369311221</v>
+        <v>0.08668297943705297</v>
       </c>
       <c r="T15">
-        <v>0.8329986322476477</v>
+        <v>0.84059708730723</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.86797845737102</v>
+        <v>24.94883713898738</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07989928231586554</v>
+        <v>0.07973624601872352</v>
       </c>
       <c r="C16">
-        <v>166.8298257144739</v>
+        <v>165.1413835694098</v>
       </c>
       <c r="D16">
-        <v>194.1058257144739</v>
+        <v>194.4713835694099</v>
       </c>
       <c r="E16">
-        <v>-145.844</v>
+        <v>-143.79</v>
       </c>
       <c r="F16">
-        <v>28.756</v>
+        <v>30.81000000000001</v>
       </c>
       <c r="G16">
         <v>1.48</v>
@@ -2587,28 +2587,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M16">
-        <v>1.4464268</v>
+        <v>1.549743</v>
       </c>
       <c r="N16">
-        <v>34.64023986666667</v>
+        <v>34.53692366666667</v>
       </c>
       <c r="O16">
-        <v>8.313657568</v>
+        <v>8.28886168</v>
       </c>
       <c r="P16">
-        <v>26.32658229866667</v>
+        <v>26.24806198666667</v>
       </c>
       <c r="Q16">
-        <v>28.90658229866667</v>
+        <v>28.82806198666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08668297943705297</v>
+        <v>0.08706123061026297</v>
       </c>
       <c r="T16">
-        <v>0.84059708730723</v>
+        <v>0.8483743295446851</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.94883713898738</v>
+        <v>23.28558132972155</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07973624601872351</v>
+        <v>0.07957320972158147</v>
       </c>
       <c r="C17">
-        <v>165.1413835694099</v>
+        <v>163.4543209263645</v>
       </c>
       <c r="D17">
-        <v>194.4713835694099</v>
+        <v>194.8383209263645</v>
       </c>
       <c r="E17">
-        <v>-143.79</v>
+        <v>-141.736</v>
       </c>
       <c r="F17">
-        <v>30.81</v>
+        <v>32.864</v>
       </c>
       <c r="G17">
         <v>1.48</v>
@@ -2669,28 +2669,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M17">
-        <v>1.549743</v>
+        <v>1.6530592</v>
       </c>
       <c r="N17">
-        <v>34.53692366666667</v>
+        <v>34.43360746666666</v>
       </c>
       <c r="O17">
-        <v>8.28886168</v>
+        <v>8.264065791999998</v>
       </c>
       <c r="P17">
-        <v>26.24806198666667</v>
+        <v>26.16954167466667</v>
       </c>
       <c r="Q17">
-        <v>28.82806198666667</v>
+        <v>28.74954167466667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08706123061026295</v>
+        <v>0.08744848776378747</v>
       </c>
       <c r="T17">
-        <v>0.8483743295446849</v>
+        <v>0.8563367442163651</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.28558132972155</v>
+        <v>21.83023249661395</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07957320972158147</v>
+        <v>0.07941017342443941</v>
       </c>
       <c r="C18">
-        <v>163.4543209263645</v>
+        <v>161.768645608819</v>
       </c>
       <c r="D18">
-        <v>194.8383209263645</v>
+        <v>195.206645608819</v>
       </c>
       <c r="E18">
-        <v>-141.736</v>
+        <v>-139.682</v>
       </c>
       <c r="F18">
-        <v>32.864</v>
+        <v>34.91800000000001</v>
       </c>
       <c r="G18">
         <v>1.48</v>
@@ -2751,28 +2751,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M18">
-        <v>1.6530592</v>
+        <v>1.7563754</v>
       </c>
       <c r="N18">
-        <v>34.43360746666666</v>
+        <v>34.33029126666666</v>
       </c>
       <c r="O18">
-        <v>8.264065791999998</v>
+        <v>8.239269903999999</v>
       </c>
       <c r="P18">
-        <v>26.16954167466667</v>
+        <v>26.09102136266667</v>
       </c>
       <c r="Q18">
-        <v>28.74954167466667</v>
+        <v>28.67102136266666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08744848776378747</v>
+        <v>0.08784507641498725</v>
       </c>
       <c r="T18">
-        <v>0.8563367442163651</v>
+        <v>0.8644910243018205</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.83023249661395</v>
+        <v>20.54610117328372</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07941017342443941</v>
+        <v>0.07924713712729738</v>
       </c>
       <c r="C19">
-        <v>161.768645608819</v>
+        <v>160.0843654995248</v>
       </c>
       <c r="D19">
-        <v>195.206645608819</v>
+        <v>195.5763654995248</v>
       </c>
       <c r="E19">
-        <v>-139.682</v>
+        <v>-137.628</v>
       </c>
       <c r="F19">
-        <v>34.91800000000001</v>
+        <v>36.97200000000001</v>
       </c>
       <c r="G19">
         <v>1.48</v>
@@ -2833,28 +2833,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M19">
-        <v>1.7563754</v>
+        <v>1.8596916</v>
       </c>
       <c r="N19">
-        <v>34.33029126666666</v>
+        <v>34.22697506666667</v>
       </c>
       <c r="O19">
-        <v>8.239269903999999</v>
+        <v>8.214474016</v>
       </c>
       <c r="P19">
-        <v>26.09102136266667</v>
+        <v>26.01250105066667</v>
       </c>
       <c r="Q19">
-        <v>28.67102136266666</v>
+        <v>28.59250105066667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08784507641498725</v>
+        <v>0.08825133796011875</v>
       </c>
       <c r="T19">
-        <v>0.8644910243018205</v>
+        <v>0.872844189267409</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.54610117328372</v>
+        <v>19.40465110810129</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07924713712729736</v>
+        <v>0.07908410083015531</v>
       </c>
       <c r="C20">
-        <v>160.0843654995248</v>
+        <v>158.4014885410665</v>
       </c>
       <c r="D20">
-        <v>195.5763654995248</v>
+        <v>195.9474885410665</v>
       </c>
       <c r="E20">
-        <v>-137.628</v>
+        <v>-135.574</v>
       </c>
       <c r="F20">
-        <v>36.972</v>
+        <v>39.026</v>
       </c>
       <c r="G20">
         <v>1.48</v>
@@ -2915,28 +2915,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M20">
-        <v>1.8596916</v>
+        <v>1.9630078</v>
       </c>
       <c r="N20">
-        <v>34.22697506666667</v>
+        <v>34.12365886666667</v>
       </c>
       <c r="O20">
-        <v>8.214474016</v>
+        <v>8.189678127999999</v>
       </c>
       <c r="P20">
-        <v>26.01250105066667</v>
+        <v>25.93398073866667</v>
       </c>
       <c r="Q20">
-        <v>28.59250105066667</v>
+        <v>28.51398073866667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08825133796011872</v>
+        <v>0.08866763065451272</v>
       </c>
       <c r="T20">
-        <v>0.8728441892674088</v>
+        <v>0.881403605219802</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.40465110810129</v>
+        <v>18.38335368135912</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07908410083015531</v>
+        <v>0.07892106453301326</v>
       </c>
       <c r="C21">
-        <v>158.4014885410665</v>
+        <v>156.7200227364299</v>
       </c>
       <c r="D21">
-        <v>195.9474885410665</v>
+        <v>196.3200227364299</v>
       </c>
       <c r="E21">
-        <v>-135.574</v>
+        <v>-133.52</v>
       </c>
       <c r="F21">
-        <v>39.026</v>
+        <v>41.08000000000001</v>
       </c>
       <c r="G21">
         <v>1.48</v>
@@ -2997,28 +2997,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M21">
-        <v>1.9630078</v>
+        <v>2.066324</v>
       </c>
       <c r="N21">
-        <v>34.12365886666667</v>
+        <v>34.02034266666666</v>
       </c>
       <c r="O21">
-        <v>8.189678127999999</v>
+        <v>8.164882239999999</v>
       </c>
       <c r="P21">
-        <v>25.93398073866667</v>
+        <v>25.85546042666667</v>
       </c>
       <c r="Q21">
-        <v>28.51398073866667</v>
+        <v>28.43546042666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08866763065451272</v>
+        <v>0.08909433066626657</v>
       </c>
       <c r="T21">
-        <v>0.881403605219802</v>
+        <v>0.890177006571005</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.38335368135912</v>
+        <v>17.46418599729116</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07892106453301326</v>
+        <v>0.07875802823587121</v>
       </c>
       <c r="C22">
-        <v>156.7200227364299</v>
+        <v>155.039976149578</v>
       </c>
       <c r="D22">
-        <v>196.3200227364299</v>
+        <v>196.693976149578</v>
       </c>
       <c r="E22">
-        <v>-133.52</v>
+        <v>-131.466</v>
       </c>
       <c r="F22">
-        <v>41.08000000000001</v>
+        <v>43.13400000000001</v>
       </c>
       <c r="G22">
         <v>1.48</v>
@@ -3079,28 +3079,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M22">
-        <v>2.066324</v>
+        <v>2.1696402</v>
       </c>
       <c r="N22">
-        <v>34.02034266666666</v>
+        <v>33.91702646666666</v>
       </c>
       <c r="O22">
-        <v>8.164882239999999</v>
+        <v>8.140086351999999</v>
       </c>
       <c r="P22">
-        <v>25.85546042666667</v>
+        <v>25.77694011466667</v>
       </c>
       <c r="Q22">
-        <v>28.43546042666667</v>
+        <v>28.35694011466666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08909433066626657</v>
+        <v>0.08953183320996355</v>
       </c>
       <c r="T22">
-        <v>0.890177006571005</v>
+        <v>0.8991725193488207</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.46418599729116</v>
+        <v>16.63255809265825</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07875802823587121</v>
+        <v>0.07859499193872917</v>
       </c>
       <c r="C23">
-        <v>155.039976149578</v>
+        <v>153.3613569060321</v>
       </c>
       <c r="D23">
-        <v>196.693976149578</v>
+        <v>197.0693569060322</v>
       </c>
       <c r="E23">
-        <v>-131.466</v>
+        <v>-129.412</v>
       </c>
       <c r="F23">
-        <v>43.134</v>
+        <v>45.188</v>
       </c>
       <c r="G23">
         <v>1.48</v>
@@ -3161,28 +3161,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M23">
-        <v>2.1696402</v>
+        <v>2.2729564</v>
       </c>
       <c r="N23">
-        <v>33.91702646666667</v>
+        <v>33.81371026666667</v>
       </c>
       <c r="O23">
-        <v>8.140086352000001</v>
+        <v>8.115290463999999</v>
       </c>
       <c r="P23">
-        <v>25.77694011466667</v>
+        <v>25.69841980266667</v>
       </c>
       <c r="Q23">
-        <v>28.35694011466667</v>
+        <v>28.27841980266667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08953183320996355</v>
+        <v>0.08998055376760149</v>
       </c>
       <c r="T23">
-        <v>0.8991725193488207</v>
+        <v>0.9083986863004266</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.63255809265825</v>
+        <v>15.87653272481015</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07859499193872917</v>
+        <v>0.07843195564158711</v>
       </c>
       <c r="C24">
-        <v>153.3613569060321</v>
+        <v>151.6841731934612</v>
       </c>
       <c r="D24">
-        <v>197.0693569060322</v>
+        <v>197.4461731934612</v>
       </c>
       <c r="E24">
-        <v>-129.412</v>
+        <v>-127.358</v>
       </c>
       <c r="F24">
-        <v>45.188</v>
+        <v>47.242</v>
       </c>
       <c r="G24">
         <v>1.48</v>
@@ -3243,28 +3243,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M24">
-        <v>2.2729564</v>
+        <v>2.3762726</v>
       </c>
       <c r="N24">
-        <v>33.81371026666667</v>
+        <v>33.71039406666667</v>
       </c>
       <c r="O24">
-        <v>8.115290463999999</v>
+        <v>8.090494575999999</v>
       </c>
       <c r="P24">
-        <v>25.69841980266667</v>
+        <v>25.61989949066667</v>
       </c>
       <c r="Q24">
-        <v>28.27841980266667</v>
+        <v>28.19989949066667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08998055376760149</v>
+        <v>0.09044092940465859</v>
       </c>
       <c r="T24">
-        <v>0.9083986863004266</v>
+        <v>0.9178644939520743</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.87653272481015</v>
+        <v>15.18624869329666</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07843195564158711</v>
+        <v>0.07826891934444506</v>
       </c>
       <c r="C25">
-        <v>151.6841731934612</v>
+        <v>150.0084332622765</v>
       </c>
       <c r="D25">
-        <v>197.4461731934612</v>
+        <v>197.8244332622765</v>
       </c>
       <c r="E25">
-        <v>-127.358</v>
+        <v>-125.304</v>
       </c>
       <c r="F25">
-        <v>47.242</v>
+        <v>49.29600000000001</v>
       </c>
       <c r="G25">
         <v>1.48</v>
@@ -3325,28 +3325,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M25">
-        <v>2.3762726</v>
+        <v>2.4795888</v>
       </c>
       <c r="N25">
-        <v>33.71039406666667</v>
+        <v>33.60707786666666</v>
       </c>
       <c r="O25">
-        <v>8.090494575999999</v>
+        <v>8.065698687999999</v>
       </c>
       <c r="P25">
-        <v>25.61989949066667</v>
+        <v>25.54137917866667</v>
       </c>
       <c r="Q25">
-        <v>28.19989949066667</v>
+        <v>28.12137917866666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09044092940465859</v>
+        <v>0.0909134201900593</v>
       </c>
       <c r="T25">
-        <v>0.9178644939520743</v>
+        <v>0.9275794018050809</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.18624869329666</v>
+        <v>14.55348833107597</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07826891934444506</v>
+        <v>0.078105883047303</v>
       </c>
       <c r="C26">
-        <v>150.0084332622765</v>
+        <v>148.3341454262339</v>
       </c>
       <c r="D26">
-        <v>197.8244332622765</v>
+        <v>198.2041454262339</v>
       </c>
       <c r="E26">
-        <v>-125.304</v>
+        <v>-123.25</v>
       </c>
       <c r="F26">
-        <v>49.296</v>
+        <v>51.35</v>
       </c>
       <c r="G26">
         <v>1.48</v>
@@ -3407,28 +3407,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M26">
-        <v>2.4795888</v>
+        <v>2.582905</v>
       </c>
       <c r="N26">
-        <v>33.60707786666666</v>
+        <v>33.50376166666667</v>
       </c>
       <c r="O26">
-        <v>8.065698687999999</v>
+        <v>8.0409028</v>
       </c>
       <c r="P26">
-        <v>25.54137917866667</v>
+        <v>25.46285886666667</v>
       </c>
       <c r="Q26">
-        <v>28.12137917866666</v>
+        <v>28.04285886666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0909134201900593</v>
+        <v>0.09139851072973734</v>
       </c>
       <c r="T26">
-        <v>0.9275794018050809</v>
+        <v>0.9375533738675011</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.55348833107597</v>
+        <v>13.97134879783293</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.078105883047303</v>
+        <v>0.07794284675016094</v>
       </c>
       <c r="C27">
-        <v>148.3341454262339</v>
+        <v>146.6613180630432</v>
       </c>
       <c r="D27">
-        <v>198.2041454262339</v>
+        <v>198.5853180630432</v>
       </c>
       <c r="E27">
-        <v>-123.25</v>
+        <v>-121.196</v>
       </c>
       <c r="F27">
-        <v>51.35</v>
+        <v>53.404</v>
       </c>
       <c r="G27">
         <v>1.48</v>
@@ -3489,28 +3489,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M27">
-        <v>2.582905</v>
+        <v>2.6862212</v>
       </c>
       <c r="N27">
-        <v>33.50376166666667</v>
+        <v>33.40044546666667</v>
       </c>
       <c r="O27">
-        <v>8.0409028</v>
+        <v>8.016106912</v>
       </c>
       <c r="P27">
-        <v>25.46285886666667</v>
+        <v>25.38433855466667</v>
       </c>
       <c r="Q27">
-        <v>28.04285886666667</v>
+        <v>27.96433855466667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09139851072973734</v>
+        <v>0.09189671182454183</v>
       </c>
       <c r="T27">
-        <v>0.9375533738675011</v>
+        <v>0.9477969127424191</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.97134879783293</v>
+        <v>13.43398922868551</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07794284675016094</v>
+        <v>0.0777798104530189</v>
       </c>
       <c r="C28">
-        <v>146.6613180630432</v>
+        <v>144.989959614984</v>
       </c>
       <c r="D28">
-        <v>198.5853180630432</v>
+        <v>198.967959614984</v>
       </c>
       <c r="E28">
-        <v>-121.196</v>
+        <v>-119.142</v>
       </c>
       <c r="F28">
-        <v>53.404</v>
+        <v>55.45800000000001</v>
       </c>
       <c r="G28">
         <v>1.48</v>
@@ -3571,28 +3571,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M28">
-        <v>2.6862212</v>
+        <v>2.7895374</v>
       </c>
       <c r="N28">
-        <v>33.40044546666667</v>
+        <v>33.29712926666667</v>
       </c>
       <c r="O28">
-        <v>8.016106912</v>
+        <v>7.991311024</v>
       </c>
       <c r="P28">
-        <v>25.38433855466667</v>
+        <v>25.30581824266667</v>
       </c>
       <c r="Q28">
-        <v>27.96433855466667</v>
+        <v>27.88581824266667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09189671182454183</v>
+        <v>0.09240856226440947</v>
       </c>
       <c r="T28">
-        <v>0.9477969127424191</v>
+        <v>0.9583210965180199</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.43398922868551</v>
+        <v>12.93643407206753</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0777798104530189</v>
+        <v>0.07793597415587686</v>
       </c>
       <c r="C29">
-        <v>144.989959614984</v>
+        <v>142.5694181318355</v>
       </c>
       <c r="D29">
-        <v>198.967959614984</v>
+        <v>198.6014181318355</v>
       </c>
       <c r="E29">
-        <v>-119.142</v>
+        <v>-117.088</v>
       </c>
       <c r="F29">
-        <v>55.45800000000001</v>
+        <v>57.51200000000001</v>
       </c>
       <c r="G29">
         <v>1.48</v>
@@ -3653,45 +3653,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M29">
-        <v>2.7895374</v>
+        <v>2.9791216</v>
       </c>
       <c r="N29">
-        <v>33.29712926666667</v>
+        <v>33.10754506666667</v>
       </c>
       <c r="O29">
-        <v>7.991311024</v>
+        <v>7.945810816</v>
       </c>
       <c r="P29">
-        <v>25.30581824266667</v>
+        <v>25.16173425066667</v>
       </c>
       <c r="Q29">
-        <v>27.88581824266667</v>
+        <v>27.74173425066667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09240856226440947</v>
+        <v>0.09293463077205119</v>
       </c>
       <c r="T29">
-        <v>0.9583210965180199</v>
+        <v>0.9691376187318318</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>12.93643407206753</v>
+        <v>12.11319023253924</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07793597415587686</v>
+        <v>0.07778433785873481</v>
       </c>
       <c r="C30">
-        <v>142.5694181318355</v>
+        <v>140.8713140181828</v>
       </c>
       <c r="D30">
-        <v>198.6014181318355</v>
+        <v>198.9573140181828</v>
       </c>
       <c r="E30">
-        <v>-117.088</v>
+        <v>-115.034</v>
       </c>
       <c r="F30">
-        <v>57.51200000000001</v>
+        <v>59.56600000000001</v>
       </c>
       <c r="G30">
         <v>1.48</v>
@@ -3735,28 +3735,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M30">
-        <v>2.9791216</v>
+        <v>3.0855188</v>
       </c>
       <c r="N30">
-        <v>33.10754506666667</v>
+        <v>33.00114786666666</v>
       </c>
       <c r="O30">
-        <v>7.945810816</v>
+        <v>7.920275487999999</v>
       </c>
       <c r="P30">
-        <v>25.16173425066667</v>
+        <v>25.08087237866667</v>
       </c>
       <c r="Q30">
-        <v>27.74173425066667</v>
+        <v>27.66087237866667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09293463077205119</v>
+        <v>0.09347551811089411</v>
       </c>
       <c r="T30">
-        <v>0.9691376187318318</v>
+        <v>0.98025883171223</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.11319023253924</v>
+        <v>11.69549401762409</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07778433785873481</v>
+        <v>0.07763270156159274</v>
       </c>
       <c r="C31">
-        <v>140.8713140181828</v>
+        <v>139.1744877329571</v>
       </c>
       <c r="D31">
-        <v>198.9573140181828</v>
+        <v>199.3144877329571</v>
       </c>
       <c r="E31">
-        <v>-115.034</v>
+        <v>-112.98</v>
       </c>
       <c r="F31">
-        <v>59.566</v>
+        <v>61.62</v>
       </c>
       <c r="G31">
         <v>1.48</v>
@@ -3817,28 +3817,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M31">
-        <v>3.0855188</v>
+        <v>3.191916</v>
       </c>
       <c r="N31">
-        <v>33.00114786666666</v>
+        <v>32.89475066666667</v>
       </c>
       <c r="O31">
-        <v>7.920275487999999</v>
+        <v>7.89474016</v>
       </c>
       <c r="P31">
-        <v>25.08087237866667</v>
+        <v>25.00001050666667</v>
       </c>
       <c r="Q31">
-        <v>27.66087237866667</v>
+        <v>27.58001050666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09347551811089411</v>
+        <v>0.09403185937370392</v>
       </c>
       <c r="T31">
-        <v>0.98025883171223</v>
+        <v>0.9916977936349251</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.69549401762409</v>
+        <v>11.30564421703662</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07763270156159274</v>
+        <v>0.0774810652644507</v>
       </c>
       <c r="C32">
-        <v>139.1744877329571</v>
+        <v>137.4789461705148</v>
       </c>
       <c r="D32">
-        <v>199.3144877329571</v>
+        <v>199.6729461705148</v>
       </c>
       <c r="E32">
-        <v>-112.98</v>
+        <v>-110.926</v>
       </c>
       <c r="F32">
-        <v>61.62</v>
+        <v>63.674</v>
       </c>
       <c r="G32">
         <v>1.48</v>
@@ -3899,28 +3899,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M32">
-        <v>3.191916</v>
+        <v>3.2983132</v>
       </c>
       <c r="N32">
-        <v>32.89475066666667</v>
+        <v>32.78835346666666</v>
       </c>
       <c r="O32">
-        <v>7.89474016</v>
+        <v>7.869204831999999</v>
       </c>
       <c r="P32">
-        <v>25.00001050666667</v>
+        <v>24.91914863466667</v>
       </c>
       <c r="Q32">
-        <v>27.58001050666667</v>
+        <v>27.49914863466667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09403185937370392</v>
+        <v>0.09460432647021841</v>
       </c>
       <c r="T32">
-        <v>0.9916977936349251</v>
+        <v>1.003468319671322</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.30564421703662</v>
+        <v>10.94094601648705</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0774810652644507</v>
+        <v>0.07732942896730864</v>
       </c>
       <c r="C33">
-        <v>137.4789461705148</v>
+        <v>135.7846962748987</v>
       </c>
       <c r="D33">
-        <v>199.6729461705148</v>
+        <v>200.0326962748987</v>
       </c>
       <c r="E33">
-        <v>-110.926</v>
+        <v>-108.872</v>
       </c>
       <c r="F33">
-        <v>63.674</v>
+        <v>65.72800000000001</v>
       </c>
       <c r="G33">
         <v>1.48</v>
@@ -3981,28 +3981,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M33">
-        <v>3.2983132</v>
+        <v>3.4047104</v>
       </c>
       <c r="N33">
-        <v>32.78835346666666</v>
+        <v>32.68195626666667</v>
       </c>
       <c r="O33">
-        <v>7.869204831999999</v>
+        <v>7.843669504</v>
       </c>
       <c r="P33">
-        <v>24.91914863466667</v>
+        <v>24.83828676266667</v>
       </c>
       <c r="Q33">
-        <v>27.49914863466667</v>
+        <v>27.41828676266667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09460432647021841</v>
+        <v>0.09519363083427743</v>
       </c>
       <c r="T33">
-        <v>1.003468319671322</v>
+        <v>1.015585037649965</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.94094601648705</v>
+        <v>10.59904145347183</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07732942896730864</v>
+        <v>0.07717779267016658</v>
       </c>
       <c r="C34">
-        <v>135.7846962748987</v>
+        <v>134.0917450402861</v>
       </c>
       <c r="D34">
-        <v>200.0326962748987</v>
+        <v>200.3937450402861</v>
       </c>
       <c r="E34">
-        <v>-108.872</v>
+        <v>-106.818</v>
       </c>
       <c r="F34">
-        <v>65.72800000000001</v>
+        <v>67.78200000000001</v>
       </c>
       <c r="G34">
         <v>1.48</v>
@@ -4063,28 +4063,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M34">
-        <v>3.4047104</v>
+        <v>3.5111076</v>
       </c>
       <c r="N34">
-        <v>32.68195626666667</v>
+        <v>32.57555906666666</v>
       </c>
       <c r="O34">
-        <v>7.843669504</v>
+        <v>7.818134175999999</v>
       </c>
       <c r="P34">
-        <v>24.83828676266667</v>
+        <v>24.75742489066666</v>
       </c>
       <c r="Q34">
-        <v>27.41828676266667</v>
+        <v>27.33742489066666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09519363083427743</v>
+        <v>0.09580052637338299</v>
       </c>
       <c r="T34">
-        <v>1.015585037649965</v>
+        <v>1.028063448702598</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.59904145347183</v>
+        <v>10.2778583791242</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07717779267016658</v>
+        <v>0.07702615637302455</v>
       </c>
       <c r="C35">
-        <v>134.0917450402861</v>
+        <v>132.400099511442</v>
       </c>
       <c r="D35">
-        <v>200.3937450402861</v>
+        <v>200.756099511442</v>
       </c>
       <c r="E35">
-        <v>-106.818</v>
+        <v>-104.764</v>
       </c>
       <c r="F35">
-        <v>67.78200000000001</v>
+        <v>69.83600000000001</v>
       </c>
       <c r="G35">
         <v>1.48</v>
@@ -4145,28 +4145,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M35">
-        <v>3.5111076</v>
+        <v>3.617504800000001</v>
       </c>
       <c r="N35">
-        <v>32.57555906666666</v>
+        <v>32.46916186666667</v>
       </c>
       <c r="O35">
-        <v>7.818134175999999</v>
+        <v>7.792598848</v>
       </c>
       <c r="P35">
-        <v>24.75742489066666</v>
+        <v>24.67656301866667</v>
       </c>
       <c r="Q35">
-        <v>27.33742489066666</v>
+        <v>27.25656301866667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09580052637338299</v>
+        <v>0.09642581268640085</v>
       </c>
       <c r="T35">
-        <v>1.028063448702598</v>
+        <v>1.040919993423493</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.2778583791242</v>
+        <v>9.975568426797018</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07702615637302455</v>
+        <v>0.07732672007588251</v>
       </c>
       <c r="C36">
-        <v>132.400099511442</v>
+        <v>129.6291347807987</v>
       </c>
       <c r="D36">
-        <v>200.756099511442</v>
+        <v>200.0391347807987</v>
       </c>
       <c r="E36">
-        <v>-104.764</v>
+        <v>-102.71</v>
       </c>
       <c r="F36">
-        <v>69.83600000000001</v>
+        <v>71.89000000000001</v>
       </c>
       <c r="G36">
         <v>1.48</v>
@@ -4227,45 +4227,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M36">
-        <v>3.617504800000001</v>
+        <v>3.846115000000001</v>
       </c>
       <c r="N36">
-        <v>32.46916186666667</v>
+        <v>32.24055166666667</v>
       </c>
       <c r="O36">
-        <v>7.792598848</v>
+        <v>7.737732400000001</v>
       </c>
       <c r="P36">
-        <v>24.67656301866667</v>
+        <v>24.50281926666667</v>
       </c>
       <c r="Q36">
-        <v>27.25656301866667</v>
+        <v>27.08281926666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09642581268640085</v>
+        <v>0.09707033857828078</v>
       </c>
       <c r="T36">
-        <v>1.040919993423493</v>
+        <v>1.054172124135799</v>
       </c>
       <c r="U36">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>9.975568426797018</v>
+        <v>9.38262809787712</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07732672007588251</v>
+        <v>0.07718800377874045</v>
       </c>
       <c r="C37">
-        <v>129.6291347807987</v>
+        <v>127.9053912827749</v>
       </c>
       <c r="D37">
-        <v>200.0391347807987</v>
+        <v>200.369391282775</v>
       </c>
       <c r="E37">
-        <v>-102.71</v>
+        <v>-100.656</v>
       </c>
       <c r="F37">
-        <v>71.89000000000001</v>
+        <v>73.94400000000002</v>
       </c>
       <c r="G37">
         <v>1.48</v>
@@ -4309,28 +4309,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M37">
-        <v>3.846115000000001</v>
+        <v>3.956004000000001</v>
       </c>
       <c r="N37">
-        <v>32.24055166666667</v>
+        <v>32.13066266666667</v>
       </c>
       <c r="O37">
-        <v>7.737732400000001</v>
+        <v>7.71135904</v>
       </c>
       <c r="P37">
-        <v>24.50281926666667</v>
+        <v>24.41930362666667</v>
       </c>
       <c r="Q37">
-        <v>27.08281926666667</v>
+        <v>26.99930362666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09707033857828078</v>
+        <v>0.09773500590428197</v>
       </c>
       <c r="T37">
-        <v>1.054172124135799</v>
+        <v>1.067838383932865</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.38262809787712</v>
+        <v>9.121999539602756</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07718800377874047</v>
+        <v>0.07704928748159842</v>
       </c>
       <c r="C38">
-        <v>127.9053912827749</v>
+        <v>126.1827400682594</v>
       </c>
       <c r="D38">
-        <v>200.3693912827749</v>
+        <v>200.7007400682594</v>
       </c>
       <c r="E38">
-        <v>-100.656</v>
+        <v>-98.60199999999999</v>
       </c>
       <c r="F38">
-        <v>73.944</v>
+        <v>75.998</v>
       </c>
       <c r="G38">
         <v>1.48</v>
@@ -4391,28 +4391,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M38">
-        <v>3.956004</v>
+        <v>4.065893</v>
       </c>
       <c r="N38">
-        <v>32.13066266666667</v>
+        <v>32.02077366666666</v>
       </c>
       <c r="O38">
-        <v>7.71135904</v>
+        <v>7.684985679999999</v>
       </c>
       <c r="P38">
-        <v>24.41930362666667</v>
+        <v>24.33578798666667</v>
       </c>
       <c r="Q38">
-        <v>26.99930362666667</v>
+        <v>26.91578798666666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09773500590428197</v>
+        <v>0.09842077378031494</v>
       </c>
       <c r="T38">
-        <v>1.067838383932865</v>
+        <v>1.081938493247299</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.121999539602758</v>
+        <v>8.875459011505384</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07704928748159842</v>
+        <v>0.07691057118445636</v>
       </c>
       <c r="C39">
-        <v>126.1827400682594</v>
+        <v>124.4611865651219</v>
       </c>
       <c r="D39">
-        <v>200.7007400682594</v>
+        <v>201.0331865651219</v>
       </c>
       <c r="E39">
-        <v>-98.60199999999999</v>
+        <v>-96.54799999999999</v>
       </c>
       <c r="F39">
-        <v>75.998</v>
+        <v>78.05200000000001</v>
       </c>
       <c r="G39">
         <v>1.48</v>
@@ -4473,28 +4473,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M39">
-        <v>4.065893</v>
+        <v>4.175782</v>
       </c>
       <c r="N39">
-        <v>32.02077366666666</v>
+        <v>31.91088466666667</v>
       </c>
       <c r="O39">
-        <v>7.684985679999999</v>
+        <v>7.65861232</v>
       </c>
       <c r="P39">
-        <v>24.33578798666667</v>
+        <v>24.25227234666667</v>
       </c>
       <c r="Q39">
-        <v>26.91578798666666</v>
+        <v>26.83227234666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09842077378031494</v>
+        <v>0.09912866320073607</v>
       </c>
       <c r="T39">
-        <v>1.081938493247299</v>
+        <v>1.096493444797682</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.875459011505384</v>
+        <v>8.641894300676297</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07691057118445636</v>
+        <v>0.07677185488731431</v>
       </c>
       <c r="C40">
-        <v>124.4611865651219</v>
+        <v>122.7407362372553</v>
       </c>
       <c r="D40">
-        <v>201.0331865651219</v>
+        <v>201.3667362372554</v>
       </c>
       <c r="E40">
-        <v>-96.54799999999999</v>
+        <v>-94.49399999999999</v>
       </c>
       <c r="F40">
-        <v>78.05200000000001</v>
+        <v>80.10600000000001</v>
       </c>
       <c r="G40">
         <v>1.48</v>
@@ -4555,28 +4555,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M40">
-        <v>4.175782</v>
+        <v>4.285671000000001</v>
       </c>
       <c r="N40">
-        <v>31.91088466666667</v>
+        <v>31.80099566666667</v>
       </c>
       <c r="O40">
-        <v>7.65861232</v>
+        <v>7.63223896</v>
       </c>
       <c r="P40">
-        <v>24.25227234666667</v>
+        <v>24.16875670666667</v>
       </c>
       <c r="Q40">
-        <v>26.83227234666667</v>
+        <v>26.74875670666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09912866320073607</v>
+        <v>0.09985976211035133</v>
       </c>
       <c r="T40">
-        <v>1.096493444797682</v>
+        <v>1.111525607874306</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.641894300676297</v>
+        <v>8.420307267325621</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07677185488731431</v>
+        <v>0.07663313859017226</v>
       </c>
       <c r="C41">
-        <v>122.7407362372553</v>
+        <v>121.0213945848752</v>
       </c>
       <c r="D41">
-        <v>201.3667362372554</v>
+        <v>201.7013945848752</v>
       </c>
       <c r="E41">
-        <v>-94.49399999999999</v>
+        <v>-92.43999999999998</v>
       </c>
       <c r="F41">
-        <v>80.10600000000001</v>
+        <v>82.16000000000001</v>
       </c>
       <c r="G41">
         <v>1.48</v>
@@ -4637,28 +4637,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M41">
-        <v>4.285671000000001</v>
+        <v>4.395560000000001</v>
       </c>
       <c r="N41">
-        <v>31.80099566666667</v>
+        <v>31.69110666666667</v>
       </c>
       <c r="O41">
-        <v>7.63223896</v>
+        <v>7.6058656</v>
       </c>
       <c r="P41">
-        <v>24.16875670666667</v>
+        <v>24.08524106666667</v>
       </c>
       <c r="Q41">
-        <v>26.74875670666667</v>
+        <v>26.66524106666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09985976211035133</v>
+        <v>0.1006152309836204</v>
       </c>
       <c r="T41">
-        <v>1.111525607874306</v>
+        <v>1.127058843053485</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.420307267325621</v>
+        <v>8.209799585642481</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07663313859017226</v>
+        <v>0.0764944222930302</v>
       </c>
       <c r="C42">
-        <v>121.0213945848752</v>
+        <v>119.3031671448219</v>
       </c>
       <c r="D42">
-        <v>201.7013945848752</v>
+        <v>202.0371671448219</v>
       </c>
       <c r="E42">
-        <v>-92.43999999999998</v>
+        <v>-90.38599999999998</v>
       </c>
       <c r="F42">
-        <v>82.16000000000001</v>
+        <v>84.21400000000001</v>
       </c>
       <c r="G42">
         <v>1.48</v>
@@ -4719,28 +4719,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M42">
-        <v>4.395560000000001</v>
+        <v>4.505449</v>
       </c>
       <c r="N42">
-        <v>31.69110666666667</v>
+        <v>31.58121766666667</v>
       </c>
       <c r="O42">
-        <v>7.6058656</v>
+        <v>7.57949224</v>
       </c>
       <c r="P42">
-        <v>24.08524106666667</v>
+        <v>24.00172542666667</v>
       </c>
       <c r="Q42">
-        <v>26.66524106666667</v>
+        <v>26.58172542666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1006152309836204</v>
+        <v>0.1013963089712376</v>
       </c>
       <c r="T42">
-        <v>1.127058843053485</v>
+        <v>1.143118628577721</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.209799585642481</v>
+        <v>8.009560571358518</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0764944222930302</v>
+        <v>0.07635570599588816</v>
       </c>
       <c r="C43">
-        <v>119.3031671448219</v>
+        <v>117.5860594908659</v>
       </c>
       <c r="D43">
-        <v>202.0371671448219</v>
+        <v>202.3740594908659</v>
       </c>
       <c r="E43">
-        <v>-90.38599999999998</v>
+        <v>-88.33199999999998</v>
       </c>
       <c r="F43">
-        <v>84.21400000000001</v>
+        <v>86.26800000000001</v>
       </c>
       <c r="G43">
         <v>1.48</v>
@@ -4801,28 +4801,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M43">
-        <v>4.505449</v>
+        <v>4.615338</v>
       </c>
       <c r="N43">
-        <v>31.58121766666667</v>
+        <v>31.47132866666666</v>
       </c>
       <c r="O43">
-        <v>7.57949224</v>
+        <v>7.55311888</v>
       </c>
       <c r="P43">
-        <v>24.00172542666667</v>
+        <v>23.91820978666667</v>
       </c>
       <c r="Q43">
-        <v>26.58172542666667</v>
+        <v>26.49820978666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1013963089712376</v>
+        <v>0.1022043206825658</v>
       </c>
       <c r="T43">
-        <v>1.143118628577721</v>
+        <v>1.15973219980969</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.009560571358518</v>
+        <v>7.818856748230934</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07635570599588816</v>
+        <v>0.0762169896987461</v>
       </c>
       <c r="C44">
-        <v>117.5860594908659</v>
+        <v>115.8700772340165</v>
       </c>
       <c r="D44">
-        <v>202.3740594908659</v>
+        <v>202.7120772340165</v>
       </c>
       <c r="E44">
-        <v>-88.33199999999999</v>
+        <v>-86.27799999999999</v>
       </c>
       <c r="F44">
-        <v>86.268</v>
+        <v>88.322</v>
       </c>
       <c r="G44">
         <v>1.48</v>
@@ -4883,28 +4883,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M44">
-        <v>4.615338</v>
+        <v>4.725227</v>
       </c>
       <c r="N44">
-        <v>31.47132866666666</v>
+        <v>31.36143966666667</v>
       </c>
       <c r="O44">
-        <v>7.55311888</v>
+        <v>7.52674552</v>
       </c>
       <c r="P44">
-        <v>23.91820978666667</v>
+        <v>23.83469414666667</v>
       </c>
       <c r="Q44">
-        <v>26.49820978666666</v>
+        <v>26.41469414666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1022043206825658</v>
+        <v>0.1030406836820107</v>
       </c>
       <c r="T44">
-        <v>1.159732199809689</v>
+        <v>1.176928703365586</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.818856748230934</v>
+        <v>7.637022870365098</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0762169896987461</v>
+        <v>0.07634579340160405</v>
       </c>
       <c r="C45">
-        <v>115.8700772340165</v>
+        <v>113.5021766591261</v>
       </c>
       <c r="D45">
-        <v>202.7120772340165</v>
+        <v>202.3981766591262</v>
       </c>
       <c r="E45">
-        <v>-86.27799999999999</v>
+        <v>-84.22399999999999</v>
       </c>
       <c r="F45">
-        <v>88.322</v>
+        <v>90.376</v>
       </c>
       <c r="G45">
         <v>1.48</v>
@@ -4965,45 +4965,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M45">
-        <v>4.725227</v>
+        <v>4.9074168</v>
       </c>
       <c r="N45">
-        <v>31.36143966666667</v>
+        <v>31.17924986666667</v>
       </c>
       <c r="O45">
-        <v>7.52674552</v>
+        <v>7.483019968</v>
       </c>
       <c r="P45">
-        <v>23.83469414666667</v>
+        <v>23.69622989866667</v>
       </c>
       <c r="Q45">
-        <v>26.41469414666667</v>
+        <v>26.27622989866666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1030406836820107</v>
+        <v>0.1039069167885787</v>
       </c>
       <c r="T45">
-        <v>1.176928703365586</v>
+        <v>1.194739367762765</v>
       </c>
       <c r="U45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>7.637022870365098</v>
+        <v>7.353495359649636</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07634579340160405</v>
+        <v>0.07621315710446201</v>
       </c>
       <c r="C46">
-        <v>113.5021766591261</v>
+        <v>111.771432360867</v>
       </c>
       <c r="D46">
-        <v>202.3981766591262</v>
+        <v>202.721432360867</v>
       </c>
       <c r="E46">
-        <v>-84.22399999999999</v>
+        <v>-82.16999999999999</v>
       </c>
       <c r="F46">
-        <v>90.376</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G46">
         <v>1.48</v>
@@ -5047,28 +5047,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M46">
-        <v>4.9074168</v>
+        <v>5.018949</v>
       </c>
       <c r="N46">
-        <v>31.17924986666667</v>
+        <v>31.06771766666667</v>
       </c>
       <c r="O46">
-        <v>7.483019968</v>
+        <v>7.45625224</v>
       </c>
       <c r="P46">
-        <v>23.69622989866667</v>
+        <v>23.61146542666667</v>
       </c>
       <c r="Q46">
-        <v>26.27622989866666</v>
+        <v>26.19146542666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1039069167885787</v>
+        <v>0.10480464928084</v>
       </c>
       <c r="T46">
-        <v>1.194739367762765</v>
+        <v>1.213197692683478</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.353495359649636</v>
+        <v>7.190084351657422</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07621315710446201</v>
+        <v>0.07608052080731996</v>
       </c>
       <c r="C47">
-        <v>111.771432360867</v>
+        <v>110.0417222755445</v>
       </c>
       <c r="D47">
-        <v>202.721432360867</v>
+        <v>203.0457222755445</v>
       </c>
       <c r="E47">
-        <v>-82.16999999999999</v>
+        <v>-80.11599999999999</v>
       </c>
       <c r="F47">
-        <v>92.43000000000001</v>
+        <v>94.48400000000001</v>
       </c>
       <c r="G47">
         <v>1.48</v>
@@ -5129,28 +5129,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M47">
-        <v>5.018949</v>
+        <v>5.1304812</v>
       </c>
       <c r="N47">
-        <v>31.06771766666667</v>
+        <v>30.95618546666667</v>
       </c>
       <c r="O47">
-        <v>7.45625224</v>
+        <v>7.429484512</v>
       </c>
       <c r="P47">
-        <v>23.61146542666667</v>
+        <v>23.52670095466667</v>
       </c>
       <c r="Q47">
-        <v>26.19146542666667</v>
+        <v>26.10670095466666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.10480464928084</v>
+        <v>0.1057356311246666</v>
       </c>
       <c r="T47">
-        <v>1.213197692683478</v>
+        <v>1.232339659267921</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.190084351657422</v>
+        <v>7.033778170099652</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07608052080731996</v>
+        <v>0.07594788451017791</v>
       </c>
       <c r="C48">
-        <v>110.0417222755445</v>
+        <v>108.3130513743477</v>
       </c>
       <c r="D48">
-        <v>203.0457222755445</v>
+        <v>203.3710513743477</v>
       </c>
       <c r="E48">
-        <v>-80.11599999999999</v>
+        <v>-78.06199999999998</v>
       </c>
       <c r="F48">
-        <v>94.48400000000001</v>
+        <v>96.53800000000001</v>
       </c>
       <c r="G48">
         <v>1.48</v>
@@ -5211,28 +5211,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M48">
-        <v>5.1304812</v>
+        <v>5.2420134</v>
       </c>
       <c r="N48">
-        <v>30.95618546666667</v>
+        <v>30.84465326666666</v>
       </c>
       <c r="O48">
-        <v>7.429484512</v>
+        <v>7.402716783999999</v>
       </c>
       <c r="P48">
-        <v>23.52670095466667</v>
+        <v>23.44193648266667</v>
       </c>
       <c r="Q48">
-        <v>26.10670095466666</v>
+        <v>26.02193648266667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1057356311246666</v>
+        <v>0.1067017443588262</v>
       </c>
       <c r="T48">
-        <v>1.232339659267921</v>
+        <v>1.252203964214041</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.033778170099652</v>
+        <v>6.88412331541668</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07594788451017791</v>
+        <v>0.07581524821303585</v>
       </c>
       <c r="C49">
-        <v>108.3130513743477</v>
+        <v>106.5854246603772</v>
       </c>
       <c r="D49">
-        <v>203.3710513743477</v>
+        <v>203.6974246603772</v>
       </c>
       <c r="E49">
-        <v>-78.06199999999998</v>
+        <v>-76.00799999999998</v>
       </c>
       <c r="F49">
-        <v>96.53800000000001</v>
+        <v>98.59200000000001</v>
       </c>
       <c r="G49">
         <v>1.48</v>
@@ -5293,28 +5293,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M49">
-        <v>5.2420134</v>
+        <v>5.353545600000001</v>
       </c>
       <c r="N49">
-        <v>30.84465326666666</v>
+        <v>30.73312106666667</v>
       </c>
       <c r="O49">
-        <v>7.402716783999999</v>
+        <v>7.375949056</v>
       </c>
       <c r="P49">
-        <v>23.44193648266667</v>
+        <v>23.35717201066667</v>
       </c>
       <c r="Q49">
-        <v>26.02193648266667</v>
+        <v>25.93717201066666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1067017443588262</v>
+        <v>0.1077050157942997</v>
       </c>
       <c r="T49">
-        <v>1.252203964214041</v>
+        <v>1.272832280888858</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.88412331541668</v>
+        <v>6.740704079678832</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07581524821303585</v>
+        <v>0.07568261191589379</v>
       </c>
       <c r="C50">
-        <v>106.5854246603772</v>
+        <v>104.8588471689013</v>
       </c>
       <c r="D50">
-        <v>203.6974246603772</v>
+        <v>204.0248471689013</v>
       </c>
       <c r="E50">
-        <v>-76.008</v>
+        <v>-73.95399999999999</v>
       </c>
       <c r="F50">
-        <v>98.592</v>
+        <v>100.646</v>
       </c>
       <c r="G50">
         <v>1.48</v>
@@ -5375,28 +5375,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M50">
-        <v>5.3535456</v>
+        <v>5.4650778</v>
       </c>
       <c r="N50">
-        <v>30.73312106666667</v>
+        <v>30.62158886666667</v>
       </c>
       <c r="O50">
-        <v>7.375949056</v>
+        <v>7.349181327999999</v>
       </c>
       <c r="P50">
-        <v>23.35717201066667</v>
+        <v>23.27240753866667</v>
       </c>
       <c r="Q50">
-        <v>25.93717201066666</v>
+        <v>25.85240753866667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1077050157942997</v>
+        <v>0.1087476312076349</v>
       </c>
       <c r="T50">
-        <v>1.272832280888858</v>
+        <v>1.294269551158765</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.740704079678832</v>
+        <v>6.603138690297632</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07568261191589379</v>
+        <v>0.07554997561875175</v>
       </c>
       <c r="C51">
-        <v>104.8588471689013</v>
+        <v>103.1333239676152</v>
       </c>
       <c r="D51">
-        <v>204.0248471689013</v>
+        <v>204.3533239676152</v>
       </c>
       <c r="E51">
-        <v>-73.95399999999999</v>
+        <v>-71.89999999999999</v>
       </c>
       <c r="F51">
-        <v>100.646</v>
+        <v>102.7</v>
       </c>
       <c r="G51">
         <v>1.48</v>
@@ -5457,28 +5457,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M51">
-        <v>5.4650778</v>
+        <v>5.576610000000001</v>
       </c>
       <c r="N51">
-        <v>30.62158886666667</v>
+        <v>30.51005666666666</v>
       </c>
       <c r="O51">
-        <v>7.349181327999999</v>
+        <v>7.322413599999999</v>
       </c>
       <c r="P51">
-        <v>23.27240753866667</v>
+        <v>23.18764306666667</v>
       </c>
       <c r="Q51">
-        <v>25.85240753866667</v>
+        <v>25.76764306666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1087476312076349</v>
+        <v>0.1098319512375035</v>
       </c>
       <c r="T51">
-        <v>1.294269551158765</v>
+        <v>1.31656431223947</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.603138690297632</v>
+        <v>6.471075916491679</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07554997561875175</v>
+        <v>0.07541733932160971</v>
       </c>
       <c r="C52">
-        <v>103.1333239676152</v>
+        <v>101.4088601569025</v>
       </c>
       <c r="D52">
-        <v>204.3533239676152</v>
+        <v>204.6828601569025</v>
       </c>
       <c r="E52">
-        <v>-71.89999999999999</v>
+        <v>-69.84599999999999</v>
       </c>
       <c r="F52">
-        <v>102.7</v>
+        <v>104.754</v>
       </c>
       <c r="G52">
         <v>1.48</v>
@@ -5539,28 +5539,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M52">
-        <v>5.576610000000001</v>
+        <v>5.688142200000001</v>
       </c>
       <c r="N52">
-        <v>30.51005666666666</v>
+        <v>30.39852446666666</v>
       </c>
       <c r="O52">
-        <v>7.322413599999999</v>
+        <v>7.295645871999999</v>
       </c>
       <c r="P52">
-        <v>23.18764306666667</v>
+        <v>23.10287859466667</v>
       </c>
       <c r="Q52">
-        <v>25.76764306666666</v>
+        <v>25.68287859466667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1098319512375035</v>
+        <v>0.1109605292277749</v>
       </c>
       <c r="T52">
-        <v>1.31656431223947</v>
+        <v>1.339769063568366</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.471075916491679</v>
+        <v>6.344192074991842</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07541733932160971</v>
+        <v>0.07528470302446764</v>
       </c>
       <c r="C53">
-        <v>101.4088601569025</v>
+        <v>99.68546087009877</v>
       </c>
       <c r="D53">
-        <v>204.6828601569025</v>
+        <v>205.0134608700988</v>
       </c>
       <c r="E53">
-        <v>-69.84599999999999</v>
+        <v>-67.79199999999999</v>
       </c>
       <c r="F53">
-        <v>104.754</v>
+        <v>106.808</v>
       </c>
       <c r="G53">
         <v>1.48</v>
@@ -5621,28 +5621,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M53">
-        <v>5.688142200000001</v>
+        <v>5.799674400000001</v>
       </c>
       <c r="N53">
-        <v>30.39852446666666</v>
+        <v>30.28699226666667</v>
       </c>
       <c r="O53">
-        <v>7.295645871999999</v>
+        <v>7.268878143999999</v>
       </c>
       <c r="P53">
-        <v>23.10287859466667</v>
+        <v>23.01811412266667</v>
       </c>
       <c r="Q53">
-        <v>25.68287859466667</v>
+        <v>25.59811412266667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1109605292277749</v>
+        <v>0.1121361313009743</v>
       </c>
       <c r="T53">
-        <v>1.339769063568366</v>
+        <v>1.363940679535966</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.344192074991842</v>
+        <v>6.222188381241999</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07528470302446764</v>
+        <v>0.07555486672732561</v>
       </c>
       <c r="C54">
-        <v>99.68546087009877</v>
+        <v>96.95919224489201</v>
       </c>
       <c r="D54">
-        <v>205.0134608700988</v>
+        <v>204.341192244892</v>
       </c>
       <c r="E54">
-        <v>-67.79199999999999</v>
+        <v>-65.73799999999999</v>
       </c>
       <c r="F54">
-        <v>106.808</v>
+        <v>108.862</v>
       </c>
       <c r="G54">
         <v>1.48</v>
@@ -5703,45 +5703,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M54">
-        <v>5.799674400000001</v>
+        <v>6.020068600000001</v>
       </c>
       <c r="N54">
-        <v>30.28699226666667</v>
+        <v>30.06659806666666</v>
       </c>
       <c r="O54">
-        <v>7.268878143999999</v>
+        <v>7.215983536</v>
       </c>
       <c r="P54">
-        <v>23.01811412266667</v>
+        <v>22.85061453066666</v>
       </c>
       <c r="Q54">
-        <v>25.59811412266667</v>
+        <v>25.43061453066667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1121361313009743</v>
+        <v>0.1133617589943098</v>
       </c>
       <c r="T54">
-        <v>1.363940679535966</v>
+        <v>1.389140874906442</v>
       </c>
       <c r="U54">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>6.222188381241999</v>
+        <v>5.994394593222187</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07555486672732561</v>
+        <v>0.07542983043018354</v>
       </c>
       <c r="C55">
-        <v>96.95919224489201</v>
+        <v>95.21578054902157</v>
       </c>
       <c r="D55">
-        <v>204.341192244892</v>
+        <v>204.6517805490216</v>
       </c>
       <c r="E55">
-        <v>-65.73799999999999</v>
+        <v>-63.68399999999998</v>
       </c>
       <c r="F55">
-        <v>108.862</v>
+        <v>110.916</v>
       </c>
       <c r="G55">
         <v>1.48</v>
@@ -5785,28 +5785,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M55">
-        <v>6.020068600000001</v>
+        <v>6.1336548</v>
       </c>
       <c r="N55">
-        <v>30.06659806666666</v>
+        <v>29.95301186666666</v>
       </c>
       <c r="O55">
-        <v>7.215983536</v>
+        <v>7.188722847999999</v>
       </c>
       <c r="P55">
-        <v>22.85061453066666</v>
+        <v>22.76428901866667</v>
       </c>
       <c r="Q55">
-        <v>25.43061453066667</v>
+        <v>25.34428901866666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1133617589943098</v>
+        <v>0.1146406748482251</v>
       </c>
       <c r="T55">
-        <v>1.389140874906442</v>
+        <v>1.415436730945201</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.994394593222187</v>
+        <v>5.883387285940294</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07542983043018354</v>
+        <v>0.0753047941330415</v>
       </c>
       <c r="C56">
-        <v>95.21578054902157</v>
+        <v>93.47331444751588</v>
       </c>
       <c r="D56">
-        <v>204.6517805490216</v>
+        <v>204.9633144475159</v>
       </c>
       <c r="E56">
-        <v>-63.68399999999998</v>
+        <v>-61.62999999999998</v>
       </c>
       <c r="F56">
-        <v>110.916</v>
+        <v>112.97</v>
       </c>
       <c r="G56">
         <v>1.48</v>
@@ -5867,28 +5867,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M56">
-        <v>6.1336548</v>
+        <v>6.247241000000001</v>
       </c>
       <c r="N56">
-        <v>29.95301186666666</v>
+        <v>29.83942566666666</v>
       </c>
       <c r="O56">
-        <v>7.188722847999999</v>
+        <v>7.161462159999999</v>
       </c>
       <c r="P56">
-        <v>22.76428901866667</v>
+        <v>22.67796350666666</v>
       </c>
       <c r="Q56">
-        <v>25.34428901866666</v>
+        <v>25.25796350666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1146406748482251</v>
+        <v>0.1159764314067589</v>
       </c>
       <c r="T56">
-        <v>1.415436730945201</v>
+        <v>1.442901291696793</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.883387285940294</v>
+        <v>5.776416608014108</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0753047941330415</v>
+        <v>0.07517975783589945</v>
       </c>
       <c r="C57">
-        <v>93.47331444751588</v>
+        <v>91.73179826528941</v>
       </c>
       <c r="D57">
-        <v>204.9633144475159</v>
+        <v>205.2757982652894</v>
       </c>
       <c r="E57">
-        <v>-61.62999999999998</v>
+        <v>-59.57599999999998</v>
       </c>
       <c r="F57">
-        <v>112.97</v>
+        <v>115.024</v>
       </c>
       <c r="G57">
         <v>1.48</v>
@@ -5949,28 +5949,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M57">
-        <v>6.247241000000001</v>
+        <v>6.360827200000001</v>
       </c>
       <c r="N57">
-        <v>29.83942566666666</v>
+        <v>29.72583946666666</v>
       </c>
       <c r="O57">
-        <v>7.161462159999999</v>
+        <v>7.134201471999999</v>
       </c>
       <c r="P57">
-        <v>22.67796350666666</v>
+        <v>22.59163799466666</v>
       </c>
       <c r="Q57">
-        <v>25.25796350666666</v>
+        <v>25.17163799466666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1159764314067589</v>
+        <v>0.1173729041724988</v>
       </c>
       <c r="T57">
-        <v>1.442901291696793</v>
+        <v>1.471614241573457</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.776416608014108</v>
+        <v>5.673266311442426</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07517975783589945</v>
+        <v>0.0750547215387574</v>
       </c>
       <c r="C58">
-        <v>91.73179826528941</v>
+        <v>89.99123635367174</v>
       </c>
       <c r="D58">
-        <v>205.2757982652894</v>
+        <v>205.5892363536718</v>
       </c>
       <c r="E58">
-        <v>-59.57599999999998</v>
+        <v>-57.52199999999998</v>
       </c>
       <c r="F58">
-        <v>115.024</v>
+        <v>117.078</v>
       </c>
       <c r="G58">
         <v>1.48</v>
@@ -6031,28 +6031,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M58">
-        <v>6.360827200000001</v>
+        <v>6.474413400000001</v>
       </c>
       <c r="N58">
-        <v>29.72583946666666</v>
+        <v>29.61225326666666</v>
       </c>
       <c r="O58">
-        <v>7.134201471999999</v>
+        <v>7.106940783999999</v>
       </c>
       <c r="P58">
-        <v>22.59163799466666</v>
+        <v>22.50531248266666</v>
       </c>
       <c r="Q58">
-        <v>25.17163799466666</v>
+        <v>25.08531248266667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1173729041724988</v>
+        <v>0.1188343291599009</v>
       </c>
       <c r="T58">
-        <v>1.471614241573457</v>
+        <v>1.501662677490896</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.673266311442426</v>
+        <v>5.573735323522384</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0750547215387574</v>
+        <v>0.07492968524161535</v>
       </c>
       <c r="C59">
-        <v>89.99123635367174</v>
+        <v>88.2516330906095</v>
       </c>
       <c r="D59">
-        <v>205.5892363536718</v>
+        <v>205.9036330906095</v>
       </c>
       <c r="E59">
-        <v>-57.52199999999998</v>
+        <v>-55.46799999999998</v>
       </c>
       <c r="F59">
-        <v>117.078</v>
+        <v>119.132</v>
       </c>
       <c r="G59">
         <v>1.48</v>
@@ -6113,28 +6113,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M59">
-        <v>6.474413400000001</v>
+        <v>6.587999600000002</v>
       </c>
       <c r="N59">
-        <v>29.61225326666666</v>
+        <v>29.49866706666666</v>
       </c>
       <c r="O59">
-        <v>7.106940783999999</v>
+        <v>7.079680095999999</v>
       </c>
       <c r="P59">
-        <v>22.50531248266666</v>
+        <v>22.41898697066667</v>
       </c>
       <c r="Q59">
-        <v>25.08531248266667</v>
+        <v>24.99898697066666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1188343291599009</v>
+        <v>0.1203653458133699</v>
       </c>
       <c r="T59">
-        <v>1.501662677490896</v>
+        <v>1.533141991309166</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.573735323522384</v>
+        <v>5.477636438634066</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07492968524161536</v>
+        <v>0.07480464894447331</v>
       </c>
       <c r="C60">
-        <v>88.2516330906095</v>
+        <v>86.51299288087016</v>
       </c>
       <c r="D60">
-        <v>205.9036330906095</v>
+        <v>206.2189928808702</v>
       </c>
       <c r="E60">
-        <v>-55.468</v>
+        <v>-53.414</v>
       </c>
       <c r="F60">
-        <v>119.132</v>
+        <v>121.186</v>
       </c>
       <c r="G60">
         <v>1.48</v>
@@ -6195,28 +6195,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M60">
-        <v>6.5879996</v>
+        <v>6.7015858</v>
       </c>
       <c r="N60">
-        <v>29.49866706666667</v>
+        <v>29.38508086666667</v>
       </c>
       <c r="O60">
-        <v>7.079680096</v>
+        <v>7.052419408</v>
       </c>
       <c r="P60">
-        <v>22.41898697066667</v>
+        <v>22.33266145866667</v>
       </c>
       <c r="Q60">
-        <v>24.99898697066666</v>
+        <v>24.91266145866667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1203653458133699</v>
+        <v>0.1219710462060324</v>
       </c>
       <c r="T60">
-        <v>1.533141991309166</v>
+        <v>1.566156881411254</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.477636438634068</v>
+        <v>5.384795143063999</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07480464894447331</v>
+        <v>0.07467961264733125</v>
       </c>
       <c r="C61">
-        <v>86.51299288087016</v>
+        <v>84.77532015624773</v>
       </c>
       <c r="D61">
-        <v>206.2189928808702</v>
+        <v>206.5353201562477</v>
       </c>
       <c r="E61">
-        <v>-53.414</v>
+        <v>-51.36</v>
       </c>
       <c r="F61">
-        <v>121.186</v>
+        <v>123.24</v>
       </c>
       <c r="G61">
         <v>1.48</v>
@@ -6277,28 +6277,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M61">
-        <v>6.7015858</v>
+        <v>6.815172</v>
       </c>
       <c r="N61">
-        <v>29.38508086666667</v>
+        <v>29.27149466666667</v>
       </c>
       <c r="O61">
-        <v>7.052419408</v>
+        <v>7.025158719999999</v>
       </c>
       <c r="P61">
-        <v>22.33266145866667</v>
+        <v>22.24633594666667</v>
       </c>
       <c r="Q61">
-        <v>24.91266145866667</v>
+        <v>24.82633594666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1219710462060324</v>
+        <v>0.1236570316183281</v>
       </c>
       <c r="T61">
-        <v>1.566156881411254</v>
+        <v>1.600822516018446</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.384795143063999</v>
+        <v>5.295048557346266</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07467961264733125</v>
+        <v>0.07455457635018919</v>
       </c>
       <c r="C62">
-        <v>84.77532015624773</v>
+        <v>83.03861937577035</v>
       </c>
       <c r="D62">
-        <v>206.5353201562477</v>
+        <v>206.8526193757704</v>
       </c>
       <c r="E62">
-        <v>-51.36</v>
+        <v>-49.306</v>
       </c>
       <c r="F62">
-        <v>123.24</v>
+        <v>125.294</v>
       </c>
       <c r="G62">
         <v>1.48</v>
@@ -6359,28 +6359,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M62">
-        <v>6.815172</v>
+        <v>6.9287582</v>
       </c>
       <c r="N62">
-        <v>29.27149466666667</v>
+        <v>29.15790846666667</v>
       </c>
       <c r="O62">
-        <v>7.025158719999999</v>
+        <v>6.997898031999999</v>
       </c>
       <c r="P62">
-        <v>22.24633594666667</v>
+        <v>22.16001043466667</v>
       </c>
       <c r="Q62">
-        <v>24.82633594666667</v>
+        <v>24.74001043466667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1236570316183281</v>
+        <v>0.1254294778209979</v>
       </c>
       <c r="T62">
-        <v>1.600822516018446</v>
+        <v>1.637265875477289</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.295048557346266</v>
+        <v>5.208244482635672</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07455457635018919</v>
+        <v>0.07442954005304717</v>
       </c>
       <c r="C63">
-        <v>83.03861937577035</v>
+        <v>81.3028950259099</v>
       </c>
       <c r="D63">
-        <v>206.8526193757704</v>
+        <v>207.1708950259099</v>
       </c>
       <c r="E63">
-        <v>-49.306</v>
+        <v>-47.252</v>
       </c>
       <c r="F63">
-        <v>125.294</v>
+        <v>127.348</v>
       </c>
       <c r="G63">
         <v>1.48</v>
@@ -6441,28 +6441,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M63">
-        <v>6.9287582</v>
+        <v>7.0423444</v>
       </c>
       <c r="N63">
-        <v>29.15790846666667</v>
+        <v>29.04432226666666</v>
       </c>
       <c r="O63">
-        <v>6.997898031999999</v>
+        <v>6.970637343999999</v>
       </c>
       <c r="P63">
-        <v>22.16001043466667</v>
+        <v>22.07368492266666</v>
       </c>
       <c r="Q63">
-        <v>24.74001043466667</v>
+        <v>24.65368492266666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1254294778209979</v>
+        <v>0.1272952106659136</v>
       </c>
       <c r="T63">
-        <v>1.637265875477289</v>
+        <v>1.675627306486598</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.208244482635672</v>
+        <v>5.124240539367354</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07442954005304717</v>
+        <v>0.0743045037559051</v>
       </c>
       <c r="C64">
-        <v>81.3028950259099</v>
+        <v>79.56815162079363</v>
       </c>
       <c r="D64">
-        <v>207.1708950259099</v>
+        <v>207.4901516207937</v>
       </c>
       <c r="E64">
-        <v>-47.252</v>
+        <v>-45.19799999999998</v>
       </c>
       <c r="F64">
-        <v>127.348</v>
+        <v>129.402</v>
       </c>
       <c r="G64">
         <v>1.48</v>
@@ -6523,28 +6523,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M64">
-        <v>7.0423444</v>
+        <v>7.155930600000001</v>
       </c>
       <c r="N64">
-        <v>29.04432226666666</v>
+        <v>28.93073606666666</v>
       </c>
       <c r="O64">
-        <v>6.970637343999999</v>
+        <v>6.943376655999999</v>
       </c>
       <c r="P64">
-        <v>22.07368492266666</v>
+        <v>21.98735941066667</v>
       </c>
       <c r="Q64">
-        <v>24.65368492266666</v>
+        <v>24.56735941066667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1272952106659136</v>
+        <v>0.1292617939348786</v>
       </c>
       <c r="T64">
-        <v>1.675627306486598</v>
+        <v>1.716062328361274</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.124240539367354</v>
+        <v>5.042903387948824</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0743045037559051</v>
+        <v>0.07417946745876305</v>
       </c>
       <c r="C65">
-        <v>79.56815162079363</v>
+        <v>77.83439370241695</v>
       </c>
       <c r="D65">
-        <v>207.4901516207937</v>
+        <v>207.810393702417</v>
       </c>
       <c r="E65">
-        <v>-45.19799999999998</v>
+        <v>-43.14399999999998</v>
       </c>
       <c r="F65">
-        <v>129.402</v>
+        <v>131.456</v>
       </c>
       <c r="G65">
         <v>1.48</v>
@@ -6605,28 +6605,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M65">
-        <v>7.155930600000001</v>
+        <v>7.269516800000001</v>
       </c>
       <c r="N65">
-        <v>28.93073606666666</v>
+        <v>28.81714986666666</v>
       </c>
       <c r="O65">
-        <v>6.943376655999999</v>
+        <v>6.916115967999999</v>
       </c>
       <c r="P65">
-        <v>21.98735941066667</v>
+        <v>21.90103389866666</v>
       </c>
       <c r="Q65">
-        <v>24.56735941066667</v>
+        <v>24.48103389866667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1292617939348786</v>
+        <v>0.1313376318298974</v>
       </c>
       <c r="T65">
-        <v>1.716062328361274</v>
+        <v>1.758743740340099</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.042903387948824</v>
+        <v>4.964108022512123</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07417946745876305</v>
+        <v>0.07405443116162101</v>
       </c>
       <c r="C66">
-        <v>77.83439370241695</v>
+        <v>76.10162584085955</v>
       </c>
       <c r="D66">
-        <v>207.810393702417</v>
+        <v>208.1316258408596</v>
       </c>
       <c r="E66">
-        <v>-43.14399999999998</v>
+        <v>-41.08999999999997</v>
       </c>
       <c r="F66">
-        <v>131.456</v>
+        <v>133.51</v>
       </c>
       <c r="G66">
         <v>1.48</v>
@@ -6687,28 +6687,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M66">
-        <v>7.269516800000001</v>
+        <v>7.383103000000001</v>
       </c>
       <c r="N66">
-        <v>28.81714986666666</v>
+        <v>28.70356366666666</v>
       </c>
       <c r="O66">
-        <v>6.916115967999999</v>
+        <v>6.888855279999999</v>
       </c>
       <c r="P66">
-        <v>21.90103389866666</v>
+        <v>21.81470838666667</v>
       </c>
       <c r="Q66">
-        <v>24.48103389866667</v>
+        <v>24.39470838666666</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1313376318298974</v>
+        <v>0.1335320890332029</v>
       </c>
       <c r="T66">
-        <v>1.758743740340099</v>
+        <v>1.803864090146287</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.964108022512123</v>
+        <v>4.887737129858091</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07405443116162101</v>
+        <v>0.07392939486447894</v>
       </c>
       <c r="C67">
-        <v>76.10162584085955</v>
+        <v>74.36985263450242</v>
       </c>
       <c r="D67">
-        <v>208.1316258408596</v>
+        <v>208.4538526345025</v>
       </c>
       <c r="E67">
-        <v>-41.08999999999997</v>
+        <v>-39.03599999999997</v>
       </c>
       <c r="F67">
-        <v>133.51</v>
+        <v>135.564</v>
       </c>
       <c r="G67">
         <v>1.48</v>
@@ -6769,28 +6769,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M67">
-        <v>7.383103000000001</v>
+        <v>7.496689200000001</v>
       </c>
       <c r="N67">
-        <v>28.70356366666666</v>
+        <v>28.58997746666666</v>
       </c>
       <c r="O67">
-        <v>6.888855279999999</v>
+        <v>6.861594591999999</v>
       </c>
       <c r="P67">
-        <v>21.81470838666667</v>
+        <v>21.72838287466666</v>
       </c>
       <c r="Q67">
-        <v>24.39470838666666</v>
+        <v>24.30838287466666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1335320890332029</v>
+        <v>0.1358556319543499</v>
       </c>
       <c r="T67">
-        <v>1.803864090146287</v>
+        <v>1.851638578176366</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.887737129858091</v>
+        <v>4.813680506678423</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07392939486447894</v>
+        <v>0.0738043585673369</v>
       </c>
       <c r="C68">
-        <v>74.36985263450242</v>
+        <v>72.63907871024716</v>
       </c>
       <c r="D68">
-        <v>208.4538526345025</v>
+        <v>208.7770787102472</v>
       </c>
       <c r="E68">
-        <v>-39.03599999999997</v>
+        <v>-36.98199999999997</v>
       </c>
       <c r="F68">
-        <v>135.564</v>
+        <v>137.618</v>
       </c>
       <c r="G68">
         <v>1.48</v>
@@ -6851,28 +6851,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M68">
-        <v>7.496689200000001</v>
+        <v>7.610275400000002</v>
       </c>
       <c r="N68">
-        <v>28.58997746666666</v>
+        <v>28.47639126666666</v>
       </c>
       <c r="O68">
-        <v>6.861594591999999</v>
+        <v>6.834333903999999</v>
       </c>
       <c r="P68">
-        <v>21.72838287466666</v>
+        <v>21.64205736266666</v>
       </c>
       <c r="Q68">
-        <v>24.30838287466666</v>
+        <v>24.22205736266666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1358556319543499</v>
+        <v>0.1383199956585967</v>
       </c>
       <c r="T68">
-        <v>1.851638578176366</v>
+        <v>1.902308489723421</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.813680506678423</v>
+        <v>4.741834528966804</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0738043585673369</v>
+        <v>0.07367932227019484</v>
       </c>
       <c r="C69">
-        <v>72.63907871024716</v>
+        <v>70.90930872373787</v>
       </c>
       <c r="D69">
-        <v>208.7770787102472</v>
+        <v>209.1013087237379</v>
       </c>
       <c r="E69">
-        <v>-36.98199999999997</v>
+        <v>-34.92799999999997</v>
       </c>
       <c r="F69">
-        <v>137.618</v>
+        <v>139.672</v>
       </c>
       <c r="G69">
         <v>1.48</v>
@@ -6933,28 +6933,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M69">
-        <v>7.610275400000002</v>
+        <v>7.723861600000002</v>
       </c>
       <c r="N69">
-        <v>28.47639126666666</v>
+        <v>28.36280506666666</v>
       </c>
       <c r="O69">
-        <v>6.834333903999999</v>
+        <v>6.807073215999999</v>
       </c>
       <c r="P69">
-        <v>21.64205736266666</v>
+        <v>21.55573185066666</v>
       </c>
       <c r="Q69">
-        <v>24.22205736266666</v>
+        <v>24.13573185066667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1383199956585967</v>
+        <v>0.1409383820943589</v>
       </c>
       <c r="T69">
-        <v>1.902308489723421</v>
+        <v>1.956145270742167</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.741834528966804</v>
+        <v>4.672101668246704</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07367932227019484</v>
+        <v>0.0735542859730528</v>
       </c>
       <c r="C70">
-        <v>70.90930872373787</v>
+        <v>69.18054735958418</v>
       </c>
       <c r="D70">
-        <v>209.1013087237379</v>
+        <v>209.4265473595842</v>
       </c>
       <c r="E70">
-        <v>-34.92799999999997</v>
+        <v>-32.87399999999997</v>
       </c>
       <c r="F70">
-        <v>139.672</v>
+        <v>141.726</v>
       </c>
       <c r="G70">
         <v>1.48</v>
@@ -7015,28 +7015,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M70">
-        <v>7.723861600000002</v>
+        <v>7.837447800000001</v>
       </c>
       <c r="N70">
-        <v>28.36280506666666</v>
+        <v>28.24921886666667</v>
       </c>
       <c r="O70">
-        <v>6.807073215999999</v>
+        <v>6.779812528</v>
       </c>
       <c r="P70">
-        <v>21.55573185066666</v>
+        <v>21.46940633866667</v>
       </c>
       <c r="Q70">
-        <v>24.13573185066667</v>
+        <v>24.04940633866666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1409383820943589</v>
+        <v>0.1437256966872671</v>
       </c>
       <c r="T70">
-        <v>1.956145270742167</v>
+        <v>2.013455392471799</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.672101668246704</v>
+        <v>4.604390049866318</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0735542859730528</v>
+        <v>0.07342924967591075</v>
       </c>
       <c r="C71">
-        <v>69.18054735958418</v>
+        <v>67.45279933158733</v>
       </c>
       <c r="D71">
-        <v>209.4265473595842</v>
+        <v>209.7527993315874</v>
       </c>
       <c r="E71">
-        <v>-32.87399999999997</v>
+        <v>-30.81999999999996</v>
       </c>
       <c r="F71">
-        <v>141.726</v>
+        <v>143.78</v>
       </c>
       <c r="G71">
         <v>1.48</v>
@@ -7097,28 +7097,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M71">
-        <v>7.837447800000001</v>
+        <v>7.951034000000002</v>
       </c>
       <c r="N71">
-        <v>28.24921886666667</v>
+        <v>28.13563266666667</v>
       </c>
       <c r="O71">
-        <v>6.779812528</v>
+        <v>6.75255184</v>
       </c>
       <c r="P71">
-        <v>21.46940633866667</v>
+        <v>21.38308082666667</v>
       </c>
       <c r="Q71">
-        <v>24.04940633866666</v>
+        <v>23.96308082666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1437256966872671</v>
+        <v>0.1466988322530358</v>
       </c>
       <c r="T71">
-        <v>2.013455392471799</v>
+        <v>2.074586188983407</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.604390049866318</v>
+        <v>4.538613049153941</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07342924967591075</v>
+        <v>0.07465321337876871</v>
       </c>
       <c r="C72">
-        <v>67.45279933158733</v>
+        <v>62.24823134983467</v>
       </c>
       <c r="D72">
-        <v>209.7527993315874</v>
+        <v>206.6022313498347</v>
       </c>
       <c r="E72">
-        <v>-30.81999999999996</v>
+        <v>-28.76599999999996</v>
       </c>
       <c r="F72">
-        <v>143.78</v>
+        <v>145.834</v>
       </c>
       <c r="G72">
         <v>1.48</v>
@@ -7179,45 +7179,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M72">
-        <v>7.951034000000002</v>
+        <v>8.429205200000002</v>
       </c>
       <c r="N72">
-        <v>28.13563266666667</v>
+        <v>27.65746146666666</v>
       </c>
       <c r="O72">
-        <v>6.75255184</v>
+        <v>6.637790751999999</v>
       </c>
       <c r="P72">
-        <v>21.38308082666667</v>
+        <v>21.01967071466667</v>
       </c>
       <c r="Q72">
-        <v>23.96308082666667</v>
+        <v>23.59967071466667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1466988322530358</v>
+        <v>0.1498770116509266</v>
       </c>
       <c r="T72">
-        <v>2.074586188983407</v>
+        <v>2.139932902495816</v>
       </c>
       <c r="U72">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V72">
         <v>0.24</v>
       </c>
       <c r="W72">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.538613049153941</v>
+        <v>4.281147013322995</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07465321337876871</v>
+        <v>0.07454717708162664</v>
       </c>
       <c r="C73">
-        <v>62.2482313498347</v>
+        <v>60.46342673708892</v>
       </c>
       <c r="D73">
-        <v>206.6022313498347</v>
+        <v>206.8714267370889</v>
       </c>
       <c r="E73">
-        <v>-28.76599999999999</v>
+        <v>-26.71199999999999</v>
       </c>
       <c r="F73">
-        <v>145.834</v>
+        <v>147.888</v>
       </c>
       <c r="G73">
         <v>1.48</v>
@@ -7261,28 +7261,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M73">
-        <v>8.4292052</v>
+        <v>8.547926400000001</v>
       </c>
       <c r="N73">
-        <v>27.65746146666667</v>
+        <v>27.53874026666666</v>
       </c>
       <c r="O73">
-        <v>6.637790752</v>
+        <v>6.609297664</v>
       </c>
       <c r="P73">
-        <v>21.01967071466667</v>
+        <v>20.92944260266666</v>
       </c>
       <c r="Q73">
-        <v>23.59967071466667</v>
+        <v>23.50944260266667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1498770116509265</v>
+        <v>0.1532822038629523</v>
       </c>
       <c r="T73">
-        <v>2.139932902495815</v>
+        <v>2.209947238401967</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.281147013322996</v>
+        <v>4.221686638137953</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07454717708162664</v>
+        <v>0.07444114078448461</v>
       </c>
       <c r="C74">
-        <v>60.46342673708892</v>
+        <v>58.67932454367394</v>
       </c>
       <c r="D74">
-        <v>206.8714267370889</v>
+        <v>207.141324543674</v>
       </c>
       <c r="E74">
-        <v>-26.71199999999999</v>
+        <v>-24.65799999999999</v>
       </c>
       <c r="F74">
-        <v>147.888</v>
+        <v>149.942</v>
       </c>
       <c r="G74">
         <v>1.48</v>
@@ -7343,28 +7343,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M74">
-        <v>8.547926400000001</v>
+        <v>8.666647600000001</v>
       </c>
       <c r="N74">
-        <v>27.53874026666666</v>
+        <v>27.42001906666666</v>
       </c>
       <c r="O74">
-        <v>6.609297664</v>
+        <v>6.580804575999999</v>
       </c>
       <c r="P74">
-        <v>20.92944260266666</v>
+        <v>20.83921449066667</v>
       </c>
       <c r="Q74">
-        <v>23.50944260266667</v>
+        <v>23.41921449066667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1532822038629523</v>
+        <v>0.1569396325351281</v>
       </c>
       <c r="T74">
-        <v>2.209947238401967</v>
+        <v>2.285147821412278</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.221686638137953</v>
+        <v>4.163855314327845</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07444114078448461</v>
+        <v>0.07433510448734254</v>
       </c>
       <c r="C75">
-        <v>58.67932454367394</v>
+        <v>56.89592752244599</v>
       </c>
       <c r="D75">
-        <v>207.141324543674</v>
+        <v>207.411927522446</v>
       </c>
       <c r="E75">
-        <v>-24.65799999999999</v>
+        <v>-22.60399999999998</v>
       </c>
       <c r="F75">
-        <v>149.942</v>
+        <v>151.996</v>
       </c>
       <c r="G75">
         <v>1.48</v>
@@ -7425,28 +7425,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M75">
-        <v>8.666647600000001</v>
+        <v>8.785368800000001</v>
       </c>
       <c r="N75">
-        <v>27.42001906666666</v>
+        <v>27.30129786666667</v>
       </c>
       <c r="O75">
-        <v>6.580804575999999</v>
+        <v>6.552311487999999</v>
       </c>
       <c r="P75">
-        <v>20.83921449066667</v>
+        <v>20.74898637866666</v>
       </c>
       <c r="Q75">
-        <v>23.41921449066667</v>
+        <v>23.32898637866666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1569396325351281</v>
+        <v>0.1608784018743944</v>
       </c>
       <c r="T75">
-        <v>2.285147821412278</v>
+        <v>2.366133064654151</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.163855314327845</v>
+        <v>4.10758699926936</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07433510448734254</v>
+        <v>0.0742290681902005</v>
       </c>
       <c r="C76">
-        <v>56.89592752244599</v>
+        <v>55.11323844066501</v>
       </c>
       <c r="D76">
-        <v>207.411927522446</v>
+        <v>207.683238440665</v>
       </c>
       <c r="E76">
-        <v>-22.60399999999998</v>
+        <v>-20.54999999999998</v>
       </c>
       <c r="F76">
-        <v>151.996</v>
+        <v>154.05</v>
       </c>
       <c r="G76">
         <v>1.48</v>
@@ -7507,28 +7507,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M76">
-        <v>8.785368800000001</v>
+        <v>8.904090000000002</v>
       </c>
       <c r="N76">
-        <v>27.30129786666667</v>
+        <v>27.18257666666666</v>
       </c>
       <c r="O76">
-        <v>6.552311487999999</v>
+        <v>6.523818399999999</v>
       </c>
       <c r="P76">
-        <v>20.74898637866666</v>
+        <v>20.65875826666666</v>
       </c>
       <c r="Q76">
-        <v>23.32898637866666</v>
+        <v>23.23875826666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1608784018743944</v>
+        <v>0.165132272760802</v>
       </c>
       <c r="T76">
-        <v>2.366133064654151</v>
+        <v>2.453597127355375</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.10758699926936</v>
+        <v>4.052819172612435</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0742290681902005</v>
+        <v>0.07614463189305845</v>
       </c>
       <c r="C77">
-        <v>55.11323844066501</v>
+        <v>48.26484404329941</v>
       </c>
       <c r="D77">
-        <v>207.683238440665</v>
+        <v>202.8888440432994</v>
       </c>
       <c r="E77">
-        <v>-20.54999999999998</v>
+        <v>-18.49599999999998</v>
       </c>
       <c r="F77">
-        <v>154.05</v>
+        <v>156.104</v>
       </c>
       <c r="G77">
         <v>1.48</v>
@@ -7589,45 +7589,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M77">
-        <v>8.904090000000002</v>
+        <v>9.5691752</v>
       </c>
       <c r="N77">
-        <v>27.18257666666666</v>
+        <v>26.51749146666667</v>
       </c>
       <c r="O77">
-        <v>6.523818399999999</v>
+        <v>6.364197952</v>
       </c>
       <c r="P77">
-        <v>20.65875826666666</v>
+        <v>20.15329351466666</v>
       </c>
       <c r="Q77">
-        <v>23.23875826666666</v>
+        <v>22.73329351466666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.165132272760802</v>
+        <v>0.1697406328877435</v>
       </c>
       <c r="T77">
-        <v>2.453597127355375</v>
+        <v>2.548349861948367</v>
       </c>
       <c r="U77">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V77">
         <v>0.24</v>
       </c>
       <c r="W77">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>4.052819172612435</v>
+        <v>3.771136583084681</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07614463189305845</v>
+        <v>0.07606519559591639</v>
       </c>
       <c r="C78">
-        <v>48.26484404329941</v>
+        <v>46.40525862077666</v>
       </c>
       <c r="D78">
-        <v>202.8888440432994</v>
+        <v>203.0832586207767</v>
       </c>
       <c r="E78">
-        <v>-18.49599999999998</v>
+        <v>-16.44199999999998</v>
       </c>
       <c r="F78">
-        <v>156.104</v>
+        <v>158.158</v>
       </c>
       <c r="G78">
         <v>1.48</v>
@@ -7671,28 +7671,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M78">
-        <v>9.5691752</v>
+        <v>9.695085400000002</v>
       </c>
       <c r="N78">
-        <v>26.51749146666667</v>
+        <v>26.39158126666666</v>
       </c>
       <c r="O78">
-        <v>6.364197952</v>
+        <v>6.333979503999998</v>
       </c>
       <c r="P78">
-        <v>20.15329351466666</v>
+        <v>20.05760176266666</v>
       </c>
       <c r="Q78">
-        <v>22.73329351466666</v>
+        <v>22.63760176266666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1697406328877435</v>
+        <v>0.1747497199822452</v>
       </c>
       <c r="T78">
-        <v>2.548349861948367</v>
+        <v>2.651341964766837</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.771136583084681</v>
+        <v>3.722160783304359</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07606519559591639</v>
+        <v>0.07598575929877435</v>
       </c>
       <c r="C79">
-        <v>46.40525862077666</v>
+        <v>44.54604614415115</v>
       </c>
       <c r="D79">
-        <v>203.0832586207767</v>
+        <v>203.2780461441512</v>
       </c>
       <c r="E79">
-        <v>-16.44199999999998</v>
+        <v>-14.38799999999998</v>
       </c>
       <c r="F79">
-        <v>158.158</v>
+        <v>160.212</v>
       </c>
       <c r="G79">
         <v>1.48</v>
@@ -7753,28 +7753,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M79">
-        <v>9.695085400000002</v>
+        <v>9.820995600000002</v>
       </c>
       <c r="N79">
-        <v>26.39158126666666</v>
+        <v>26.26567106666666</v>
       </c>
       <c r="O79">
-        <v>6.333979503999998</v>
+        <v>6.303761055999999</v>
       </c>
       <c r="P79">
-        <v>20.05760176266666</v>
+        <v>19.96191001066666</v>
       </c>
       <c r="Q79">
-        <v>22.63760176266666</v>
+        <v>22.54191001066666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1747497199822452</v>
+        <v>0.1802141786307925</v>
       </c>
       <c r="T79">
-        <v>2.651341964766837</v>
+        <v>2.76369698602335</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.722160783304359</v>
+        <v>3.674440773261996</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07598575929877435</v>
+        <v>0.0759063230016323</v>
       </c>
       <c r="C80">
-        <v>44.54604614415115</v>
+        <v>42.68720768758757</v>
       </c>
       <c r="D80">
-        <v>203.2780461441512</v>
+        <v>203.4732076875876</v>
       </c>
       <c r="E80">
-        <v>-14.38799999999998</v>
+        <v>-12.33399999999997</v>
       </c>
       <c r="F80">
-        <v>160.212</v>
+        <v>162.266</v>
       </c>
       <c r="G80">
         <v>1.48</v>
@@ -7835,28 +7835,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M80">
-        <v>9.820995600000002</v>
+        <v>9.946905800000001</v>
       </c>
       <c r="N80">
-        <v>26.26567106666666</v>
+        <v>26.13976086666666</v>
       </c>
       <c r="O80">
-        <v>6.303761055999999</v>
+        <v>6.273542607999999</v>
       </c>
       <c r="P80">
-        <v>19.96191001066666</v>
+        <v>19.86621825866666</v>
       </c>
       <c r="Q80">
-        <v>22.54191001066666</v>
+        <v>22.44621825866666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1802141786307925</v>
+        <v>0.1861990619125348</v>
       </c>
       <c r="T80">
-        <v>2.76369698602335</v>
+        <v>2.886752485494768</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.674440773261996</v>
+        <v>3.627928864739692</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0759063230016323</v>
+        <v>0.07582688670449025</v>
       </c>
       <c r="C81">
-        <v>42.68720768758757</v>
+        <v>40.82874432937967</v>
       </c>
       <c r="D81">
-        <v>203.4732076875876</v>
+        <v>203.6687443293797</v>
       </c>
       <c r="E81">
-        <v>-12.33399999999997</v>
+        <v>-10.27999999999997</v>
       </c>
       <c r="F81">
-        <v>162.266</v>
+        <v>164.32</v>
       </c>
       <c r="G81">
         <v>1.48</v>
@@ -7917,28 +7917,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M81">
-        <v>9.946905800000001</v>
+        <v>10.072816</v>
       </c>
       <c r="N81">
-        <v>26.13976086666666</v>
+        <v>26.01385066666666</v>
       </c>
       <c r="O81">
-        <v>6.273542607999999</v>
+        <v>6.243324159999998</v>
       </c>
       <c r="P81">
-        <v>19.86621825866666</v>
+        <v>19.77052650666666</v>
       </c>
       <c r="Q81">
-        <v>22.44621825866666</v>
+        <v>22.35052650666666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1861990619125348</v>
+        <v>0.1927824335224513</v>
       </c>
       <c r="T81">
-        <v>2.886752485494768</v>
+        <v>3.022113534913329</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.627928864739692</v>
+        <v>3.582579753930446</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07582688670449025</v>
+        <v>0.07574745040734819</v>
       </c>
       <c r="C82">
-        <v>40.82874432937967</v>
+        <v>38.97065715197004</v>
       </c>
       <c r="D82">
-        <v>203.6687443293797</v>
+        <v>203.8646571519701</v>
       </c>
       <c r="E82">
-        <v>-10.27999999999997</v>
+        <v>-8.225999999999971</v>
       </c>
       <c r="F82">
-        <v>164.32</v>
+        <v>166.374</v>
       </c>
       <c r="G82">
         <v>1.48</v>
@@ -7999,28 +7999,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M82">
-        <v>10.072816</v>
+        <v>10.1987262</v>
       </c>
       <c r="N82">
-        <v>26.01385066666666</v>
+        <v>25.88794046666666</v>
       </c>
       <c r="O82">
-        <v>6.243324159999998</v>
+        <v>6.213105711999999</v>
       </c>
       <c r="P82">
-        <v>19.77052650666666</v>
+        <v>19.67483475466666</v>
       </c>
       <c r="Q82">
-        <v>22.35052650666666</v>
+        <v>22.25483475466666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1927824335224513</v>
+        <v>0.2000587916176221</v>
       </c>
       <c r="T82">
-        <v>3.022113534913329</v>
+        <v>3.171723115849632</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.582579753930446</v>
+        <v>3.538350374252293</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07574745040734819</v>
+        <v>0.07741297411020615</v>
       </c>
       <c r="C83">
-        <v>38.97065715197004</v>
+        <v>32.88632908783094</v>
       </c>
       <c r="D83">
-        <v>203.8646571519701</v>
+        <v>199.834329087831</v>
       </c>
       <c r="E83">
-        <v>-8.225999999999971</v>
+        <v>-6.171999999999969</v>
       </c>
       <c r="F83">
-        <v>166.374</v>
+        <v>168.428</v>
       </c>
       <c r="G83">
         <v>1.48</v>
@@ -8081,45 +8081,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M83">
-        <v>10.1987262</v>
+        <v>10.7962348</v>
       </c>
       <c r="N83">
-        <v>25.88794046666666</v>
+        <v>25.29043186666667</v>
       </c>
       <c r="O83">
-        <v>6.213105711999999</v>
+        <v>6.069703647999999</v>
       </c>
       <c r="P83">
-        <v>19.67483475466666</v>
+        <v>19.22072821866666</v>
       </c>
       <c r="Q83">
-        <v>22.25483475466666</v>
+        <v>21.80072821866666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2000587916176221</v>
+        <v>0.2081436339455898</v>
       </c>
       <c r="T83">
-        <v>3.171723115849632</v>
+        <v>3.337955983556636</v>
       </c>
       <c r="U83">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V83">
         <v>0.24</v>
       </c>
       <c r="W83">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.538350374252293</v>
+        <v>3.342523327361004</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07741297411020615</v>
+        <v>0.07735481781306409</v>
       </c>
       <c r="C84">
-        <v>32.88632908783094</v>
+        <v>30.9703720865395</v>
       </c>
       <c r="D84">
-        <v>199.834329087831</v>
+        <v>199.9723720865395</v>
       </c>
       <c r="E84">
-        <v>-6.171999999999969</v>
+        <v>-4.117999999999967</v>
       </c>
       <c r="F84">
-        <v>168.428</v>
+        <v>170.482</v>
       </c>
       <c r="G84">
         <v>1.48</v>
@@ -8163,28 +8163,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M84">
-        <v>10.7962348</v>
+        <v>10.9278962</v>
       </c>
       <c r="N84">
-        <v>25.29043186666667</v>
+        <v>25.15877046666666</v>
       </c>
       <c r="O84">
-        <v>6.069703647999999</v>
+        <v>6.038104911999999</v>
       </c>
       <c r="P84">
-        <v>19.22072821866666</v>
+        <v>19.12066555466667</v>
       </c>
       <c r="Q84">
-        <v>21.80072821866666</v>
+        <v>21.70066555466666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2081436339455898</v>
+        <v>0.2171796341944948</v>
       </c>
       <c r="T84">
-        <v>3.337955983556636</v>
+        <v>3.52374565922917</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.342523327361004</v>
+        <v>3.302251961971112</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07735481781306409</v>
+        <v>0.07729666151592204</v>
       </c>
       <c r="C85">
-        <v>30.9703720865395</v>
+        <v>29.05460593375969</v>
       </c>
       <c r="D85">
-        <v>199.9723720865395</v>
+        <v>200.1106059337597</v>
       </c>
       <c r="E85">
-        <v>-4.117999999999967</v>
+        <v>-2.063999999999965</v>
       </c>
       <c r="F85">
-        <v>170.482</v>
+        <v>172.536</v>
       </c>
       <c r="G85">
         <v>1.48</v>
@@ -8245,28 +8245,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M85">
-        <v>10.9278962</v>
+        <v>11.0595576</v>
       </c>
       <c r="N85">
-        <v>25.15877046666666</v>
+        <v>25.02710906666666</v>
       </c>
       <c r="O85">
-        <v>6.038104911999999</v>
+        <v>6.006506175999998</v>
       </c>
       <c r="P85">
-        <v>19.12066555466667</v>
+        <v>19.02060289066666</v>
       </c>
       <c r="Q85">
-        <v>21.70066555466666</v>
+        <v>21.60060289066666</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2171796341944948</v>
+        <v>0.2273451344745129</v>
       </c>
       <c r="T85">
-        <v>3.52374565922917</v>
+        <v>3.732759044360771</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.302251961971112</v>
+        <v>3.262939438614313</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07729666151592204</v>
+        <v>0.07723850521878001</v>
       </c>
       <c r="C86">
-        <v>29.05460593375972</v>
+        <v>27.13903102554585</v>
       </c>
       <c r="D86">
-        <v>200.1106059337597</v>
+        <v>200.2490310255459</v>
       </c>
       <c r="E86">
-        <v>-2.063999999999993</v>
+        <v>-0.009999999999990905</v>
       </c>
       <c r="F86">
-        <v>172.536</v>
+        <v>174.59</v>
       </c>
       <c r="G86">
         <v>1.48</v>
@@ -8327,28 +8327,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M86">
-        <v>11.0595576</v>
+        <v>11.191219</v>
       </c>
       <c r="N86">
-        <v>25.02710906666666</v>
+        <v>24.89544766666667</v>
       </c>
       <c r="O86">
-        <v>6.006506175999999</v>
+        <v>5.97490744</v>
       </c>
       <c r="P86">
-        <v>19.02060289066667</v>
+        <v>18.92054022666667</v>
       </c>
       <c r="Q86">
-        <v>21.60060289066666</v>
+        <v>21.50054022666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2273451344745128</v>
+        <v>0.2388660347918667</v>
       </c>
       <c r="T86">
-        <v>3.732759044360769</v>
+        <v>3.96964088084325</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.262939438614313</v>
+        <v>3.224551915807087</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07723850521878001</v>
+        <v>0.07718034892163794</v>
       </c>
       <c r="C87">
-        <v>27.13903102554585</v>
+        <v>25.22364775904896</v>
       </c>
       <c r="D87">
-        <v>200.2490310255459</v>
+        <v>200.387647759049</v>
       </c>
       <c r="E87">
-        <v>-0.009999999999990905</v>
+        <v>2.044000000000011</v>
       </c>
       <c r="F87">
-        <v>174.59</v>
+        <v>176.644</v>
       </c>
       <c r="G87">
         <v>1.48</v>
@@ -8409,28 +8409,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M87">
-        <v>11.191219</v>
+        <v>11.3228804</v>
       </c>
       <c r="N87">
-        <v>24.89544766666667</v>
+        <v>24.76378626666666</v>
       </c>
       <c r="O87">
-        <v>5.97490744</v>
+        <v>5.943308703999999</v>
       </c>
       <c r="P87">
-        <v>18.92054022666667</v>
+        <v>18.82047756266666</v>
       </c>
       <c r="Q87">
-        <v>21.50054022666666</v>
+        <v>21.40047756266667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2388660347918667</v>
+        <v>0.2520327780116995</v>
       </c>
       <c r="T87">
-        <v>3.96964088084325</v>
+        <v>4.240362979680369</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.224551915807087</v>
+        <v>3.187057126088399</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07718034892163794</v>
+        <v>0.07712219262449591</v>
       </c>
       <c r="C88">
-        <v>25.22364775904896</v>
+        <v>23.3084565325203</v>
       </c>
       <c r="D88">
-        <v>200.387647759049</v>
+        <v>200.5264565325203</v>
       </c>
       <c r="E88">
-        <v>2.044000000000011</v>
+        <v>4.098000000000013</v>
       </c>
       <c r="F88">
-        <v>176.644</v>
+        <v>178.698</v>
       </c>
       <c r="G88">
         <v>1.48</v>
@@ -8491,28 +8491,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M88">
-        <v>11.3228804</v>
+        <v>11.4545418</v>
       </c>
       <c r="N88">
-        <v>24.76378626666666</v>
+        <v>24.63212486666666</v>
       </c>
       <c r="O88">
-        <v>5.943308703999999</v>
+        <v>5.911709967999999</v>
       </c>
       <c r="P88">
-        <v>18.82047756266666</v>
+        <v>18.72041489866666</v>
       </c>
       <c r="Q88">
-        <v>21.40047756266667</v>
+        <v>21.30041489866667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2520327780116995</v>
+        <v>0.2672251740345838</v>
       </c>
       <c r="T88">
-        <v>4.240362979680369</v>
+        <v>4.552734632184739</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.187057126088399</v>
+        <v>3.150424285558648</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07712219262449591</v>
+        <v>0.07706403632735384</v>
       </c>
       <c r="C89">
-        <v>23.3084565325203</v>
+        <v>21.3934577453156</v>
       </c>
       <c r="D89">
-        <v>200.5264565325203</v>
+        <v>200.6654577453156</v>
       </c>
       <c r="E89">
-        <v>4.098000000000013</v>
+        <v>6.152000000000015</v>
       </c>
       <c r="F89">
-        <v>178.698</v>
+        <v>180.752</v>
       </c>
       <c r="G89">
         <v>1.48</v>
@@ -8573,28 +8573,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M89">
-        <v>11.4545418</v>
+        <v>11.5862032</v>
       </c>
       <c r="N89">
-        <v>24.63212486666666</v>
+        <v>24.50046346666667</v>
       </c>
       <c r="O89">
-        <v>5.911709967999999</v>
+        <v>5.880111232</v>
       </c>
       <c r="P89">
-        <v>18.72041489866666</v>
+        <v>18.62035223466667</v>
       </c>
       <c r="Q89">
-        <v>21.30041489866667</v>
+        <v>21.20035223466667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2672251740345838</v>
+        <v>0.284949636061282</v>
       </c>
       <c r="T89">
-        <v>4.552734632184739</v>
+        <v>4.917168226773171</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.150424285558648</v>
+        <v>3.11462400958639</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07706403632735384</v>
+        <v>0.0770058800302118</v>
       </c>
       <c r="C90">
-        <v>21.3934577453156</v>
+        <v>19.47865179789841</v>
       </c>
       <c r="D90">
-        <v>200.6654577453156</v>
+        <v>200.8046517978984</v>
       </c>
       <c r="E90">
-        <v>6.152000000000015</v>
+        <v>8.206000000000017</v>
       </c>
       <c r="F90">
-        <v>180.752</v>
+        <v>182.806</v>
       </c>
       <c r="G90">
         <v>1.48</v>
@@ -8655,28 +8655,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M90">
-        <v>11.5862032</v>
+        <v>11.7178646</v>
       </c>
       <c r="N90">
-        <v>24.50046346666667</v>
+        <v>24.36880206666666</v>
       </c>
       <c r="O90">
-        <v>5.880111232</v>
+        <v>5.848512495999999</v>
       </c>
       <c r="P90">
-        <v>18.62035223466667</v>
+        <v>18.52028957066667</v>
       </c>
       <c r="Q90">
-        <v>21.20035223466667</v>
+        <v>21.10028957066667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.284949636061282</v>
+        <v>0.30589672754738</v>
       </c>
       <c r="T90">
-        <v>4.917168226773171</v>
+        <v>5.347862474923135</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.11462400958639</v>
+        <v>3.079628234197779</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0770058800302118</v>
+        <v>0.07694772373306974</v>
       </c>
       <c r="C91">
-        <v>19.47865179789841</v>
+        <v>17.56403909184445</v>
       </c>
       <c r="D91">
-        <v>200.8046517978984</v>
+        <v>200.9440390918445</v>
       </c>
       <c r="E91">
-        <v>8.206000000000017</v>
+        <v>10.26000000000002</v>
       </c>
       <c r="F91">
-        <v>182.806</v>
+        <v>184.86</v>
       </c>
       <c r="G91">
         <v>1.48</v>
@@ -8737,28 +8737,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M91">
-        <v>11.7178646</v>
+        <v>11.849526</v>
       </c>
       <c r="N91">
-        <v>24.36880206666666</v>
+        <v>24.23714066666667</v>
       </c>
       <c r="O91">
-        <v>5.848512495999999</v>
+        <v>5.816913759999999</v>
       </c>
       <c r="P91">
-        <v>18.52028957066667</v>
+        <v>18.42022690666667</v>
       </c>
       <c r="Q91">
-        <v>21.10028957066667</v>
+        <v>21.00022690666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.30589672754738</v>
+        <v>0.3310332373306975</v>
       </c>
       <c r="T91">
-        <v>5.347862474923135</v>
+        <v>5.864695572703093</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.079628234197779</v>
+        <v>3.045410142706693</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07694772373306974</v>
+        <v>0.0768895674359277</v>
       </c>
       <c r="C92">
-        <v>17.56403909184445</v>
+        <v>15.64962002984501</v>
       </c>
       <c r="D92">
-        <v>200.9440390918445</v>
+        <v>201.083620029845</v>
       </c>
       <c r="E92">
-        <v>10.26000000000002</v>
+        <v>12.31400000000002</v>
       </c>
       <c r="F92">
-        <v>184.86</v>
+        <v>186.914</v>
       </c>
       <c r="G92">
         <v>1.48</v>
@@ -8819,28 +8819,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M92">
-        <v>11.849526</v>
+        <v>11.9811874</v>
       </c>
       <c r="N92">
-        <v>24.23714066666667</v>
+        <v>24.10547926666666</v>
       </c>
       <c r="O92">
-        <v>5.816913759999999</v>
+        <v>5.785315023999999</v>
       </c>
       <c r="P92">
-        <v>18.42022690666667</v>
+        <v>18.32016424266666</v>
       </c>
       <c r="Q92">
-        <v>21.00022690666667</v>
+        <v>20.90016424266666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3310332373306975</v>
+        <v>0.3617556381769745</v>
       </c>
       <c r="T92">
-        <v>5.864695572703093</v>
+        <v>6.496380469989708</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.045410142706693</v>
+        <v>3.011944097182443</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0768895674359277</v>
+        <v>0.08228517113878565</v>
       </c>
       <c r="C93">
-        <v>15.64962002984501</v>
+        <v>1.4212234464392</v>
       </c>
       <c r="D93">
-        <v>201.083620029845</v>
+        <v>188.9092234464392</v>
       </c>
       <c r="E93">
-        <v>12.31400000000002</v>
+        <v>14.36800000000002</v>
       </c>
       <c r="F93">
-        <v>186.914</v>
+        <v>188.968</v>
       </c>
       <c r="G93">
         <v>1.48</v>
@@ -8901,45 +8901,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M93">
-        <v>11.9811874</v>
+        <v>13.5867992</v>
       </c>
       <c r="N93">
-        <v>24.10547926666666</v>
+        <v>22.49986746666666</v>
       </c>
       <c r="O93">
-        <v>5.785315023999999</v>
+        <v>5.399968191999999</v>
       </c>
       <c r="P93">
-        <v>18.32016424266666</v>
+        <v>17.09989927466667</v>
       </c>
       <c r="Q93">
-        <v>20.90016424266666</v>
+        <v>19.67989927466667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3617556381769745</v>
+        <v>0.4001586392348208</v>
       </c>
       <c r="T93">
-        <v>6.496380469989708</v>
+        <v>7.285986591597978</v>
       </c>
       <c r="U93">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V93">
         <v>0.24</v>
       </c>
       <c r="W93">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y93">
-        <v>3.011944097182443</v>
+        <v>2.656009420281022</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08228517113878565</v>
+        <v>0.0822862948416436</v>
       </c>
       <c r="C94">
-        <v>1.4212234464392</v>
+        <v>-0.6351584884071713</v>
       </c>
       <c r="D94">
-        <v>188.9092234464392</v>
+        <v>188.9068415115929</v>
       </c>
       <c r="E94">
-        <v>14.36800000000002</v>
+        <v>16.42200000000003</v>
       </c>
       <c r="F94">
-        <v>188.968</v>
+        <v>191.022</v>
       </c>
       <c r="G94">
         <v>1.48</v>
@@ -8983,28 +8983,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M94">
-        <v>13.5867992</v>
+        <v>13.7344818</v>
       </c>
       <c r="N94">
-        <v>22.49986746666666</v>
+        <v>22.35218486666666</v>
       </c>
       <c r="O94">
-        <v>5.399968191999999</v>
+        <v>5.364524367999999</v>
       </c>
       <c r="P94">
-        <v>17.09989927466667</v>
+        <v>16.98766049866666</v>
       </c>
       <c r="Q94">
-        <v>19.67989927466667</v>
+        <v>19.56766049866666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4001586392348208</v>
+        <v>0.4495339263091945</v>
       </c>
       <c r="T94">
-        <v>7.285986591597978</v>
+        <v>8.301194462237181</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.656009420281022</v>
+        <v>2.627450179202731</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0822862948416436</v>
+        <v>0.08228741854450156</v>
       </c>
       <c r="C95">
-        <v>-0.6351584884071713</v>
+        <v>-2.691540363187244</v>
       </c>
       <c r="D95">
-        <v>188.9068415115929</v>
+        <v>188.9044596368128</v>
       </c>
       <c r="E95">
-        <v>16.42200000000003</v>
+        <v>18.47600000000003</v>
       </c>
       <c r="F95">
-        <v>191.022</v>
+        <v>193.076</v>
       </c>
       <c r="G95">
         <v>1.48</v>
@@ -9065,28 +9065,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M95">
-        <v>13.7344818</v>
+        <v>13.8821644</v>
       </c>
       <c r="N95">
-        <v>22.35218486666666</v>
+        <v>22.20450226666667</v>
       </c>
       <c r="O95">
-        <v>5.364524367999999</v>
+        <v>5.329080543999999</v>
       </c>
       <c r="P95">
-        <v>16.98766049866666</v>
+        <v>16.87542172266667</v>
       </c>
       <c r="Q95">
-        <v>19.56766049866666</v>
+        <v>19.45542172266666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4495339263091945</v>
+        <v>0.5153676424083595</v>
       </c>
       <c r="T95">
-        <v>8.301194462237181</v>
+        <v>9.654804956422787</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.627450179202731</v>
+        <v>2.599498581551639</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08228741854450156</v>
+        <v>0.0822885422473595</v>
       </c>
       <c r="C96">
-        <v>-2.691540363187244</v>
+        <v>-4.747922177903234</v>
       </c>
       <c r="D96">
-        <v>188.9044596368128</v>
+        <v>188.9020778220968</v>
       </c>
       <c r="E96">
-        <v>18.47600000000003</v>
+        <v>20.53000000000003</v>
       </c>
       <c r="F96">
-        <v>193.076</v>
+        <v>195.13</v>
       </c>
       <c r="G96">
         <v>1.48</v>
@@ -9147,28 +9147,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M96">
-        <v>13.8821644</v>
+        <v>14.029847</v>
       </c>
       <c r="N96">
-        <v>22.20450226666667</v>
+        <v>22.05681966666666</v>
       </c>
       <c r="O96">
-        <v>5.329080543999999</v>
+        <v>5.293636719999999</v>
       </c>
       <c r="P96">
-        <v>16.87542172266667</v>
+        <v>16.76318294666666</v>
       </c>
       <c r="Q96">
-        <v>19.45542172266666</v>
+        <v>19.34318294666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5153676424083595</v>
+        <v>0.6075348449471906</v>
       </c>
       <c r="T96">
-        <v>9.654804956422787</v>
+        <v>11.54985964828264</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.599498581551639</v>
+        <v>2.572135438587938</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0822885422473595</v>
+        <v>0.08228966595021744</v>
       </c>
       <c r="C97">
-        <v>-4.747922177903234</v>
+        <v>-6.804303932557417</v>
       </c>
       <c r="D97">
-        <v>188.9020778220968</v>
+        <v>188.8996960674426</v>
       </c>
       <c r="E97">
-        <v>20.53000000000003</v>
+        <v>22.58400000000003</v>
       </c>
       <c r="F97">
-        <v>195.13</v>
+        <v>197.184</v>
       </c>
       <c r="G97">
         <v>1.48</v>
@@ -9229,28 +9229,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M97">
-        <v>14.029847</v>
+        <v>14.1775296</v>
       </c>
       <c r="N97">
-        <v>22.05681966666666</v>
+        <v>21.90913706666666</v>
       </c>
       <c r="O97">
-        <v>5.293636719999999</v>
+        <v>5.258192895999999</v>
       </c>
       <c r="P97">
-        <v>16.76318294666666</v>
+        <v>16.65094417066666</v>
       </c>
       <c r="Q97">
-        <v>19.34318294666667</v>
+        <v>19.23094417066666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6075348449471906</v>
+        <v>0.7457856487554373</v>
       </c>
       <c r="T97">
-        <v>11.54985964828264</v>
+        <v>14.39244168607241</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.572135438587938</v>
+        <v>2.545342361102646</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08228966595021744</v>
+        <v>0.0822907896530754</v>
       </c>
       <c r="C98">
-        <v>-6.804303932557389</v>
+        <v>-8.860685627152094</v>
       </c>
       <c r="D98">
-        <v>188.8996960674426</v>
+        <v>188.8973143728479</v>
       </c>
       <c r="E98">
-        <v>22.584</v>
+        <v>24.63800000000001</v>
       </c>
       <c r="F98">
-        <v>197.184</v>
+        <v>199.238</v>
       </c>
       <c r="G98">
         <v>1.48</v>
@@ -9311,28 +9311,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M98">
-        <v>14.1775296</v>
+        <v>14.3252122</v>
       </c>
       <c r="N98">
-        <v>21.90913706666667</v>
+        <v>21.76145446666666</v>
       </c>
       <c r="O98">
-        <v>5.258192896</v>
+        <v>5.222749071999999</v>
       </c>
       <c r="P98">
-        <v>16.65094417066667</v>
+        <v>16.53870539466666</v>
       </c>
       <c r="Q98">
-        <v>19.23094417066667</v>
+        <v>19.11870539466666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7457856487554354</v>
+        <v>0.9762036551025123</v>
       </c>
       <c r="T98">
-        <v>14.39244168607237</v>
+        <v>19.13007841572198</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.545342361102647</v>
+        <v>2.519101718204682</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0822907896530754</v>
+        <v>0.08519663335593335</v>
       </c>
       <c r="C99">
-        <v>-8.860685627152094</v>
+        <v>-16.87909452962961</v>
       </c>
       <c r="D99">
-        <v>188.8973143728479</v>
+        <v>182.9329054703704</v>
       </c>
       <c r="E99">
-        <v>24.63800000000001</v>
+        <v>26.69200000000001</v>
       </c>
       <c r="F99">
-        <v>199.238</v>
+        <v>201.292</v>
       </c>
       <c r="G99">
         <v>1.48</v>
@@ -9393,45 +9393,45 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M99">
-        <v>14.3252122</v>
+        <v>15.2579336</v>
       </c>
       <c r="N99">
-        <v>21.76145446666666</v>
+        <v>20.82873306666666</v>
       </c>
       <c r="O99">
-        <v>5.222749071999999</v>
+        <v>4.998895935999999</v>
       </c>
       <c r="P99">
-        <v>16.53870539466666</v>
+        <v>15.82983713066666</v>
       </c>
       <c r="Q99">
-        <v>19.11870539466666</v>
+        <v>18.40983713066667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9762036551025123</v>
+        <v>1.437039667796666</v>
       </c>
       <c r="T99">
-        <v>19.13007841572198</v>
+        <v>28.60535187502118</v>
       </c>
       <c r="U99">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V99">
         <v>0.24</v>
       </c>
       <c r="W99">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y99">
-        <v>2.519101718204682</v>
+        <v>2.36510838313431</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08519663335593335</v>
+        <v>0.0852273970587913</v>
       </c>
       <c r="C100">
-        <v>-16.87909452962961</v>
+        <v>-18.99422456744514</v>
       </c>
       <c r="D100">
-        <v>182.9329054703704</v>
+        <v>182.8717754325549</v>
       </c>
       <c r="E100">
-        <v>26.69200000000001</v>
+        <v>28.74600000000001</v>
       </c>
       <c r="F100">
-        <v>201.292</v>
+        <v>203.346</v>
       </c>
       <c r="G100">
         <v>1.48</v>
@@ -9475,28 +9475,28 @@
         <v>36.08666666666667</v>
       </c>
       <c r="M100">
-        <v>15.2579336</v>
+        <v>15.4136268</v>
       </c>
       <c r="N100">
-        <v>20.82873306666666</v>
+        <v>20.67303986666666</v>
       </c>
       <c r="O100">
-        <v>4.998895935999999</v>
+        <v>4.961529567999999</v>
       </c>
       <c r="P100">
-        <v>15.82983713066666</v>
+        <v>15.71151029866666</v>
       </c>
       <c r="Q100">
-        <v>18.40983713066667</v>
+        <v>18.29151029866667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.437039667796666</v>
+        <v>2.819547705879127</v>
       </c>
       <c r="T100">
-        <v>28.60535187502118</v>
+        <v>57.03117225291879</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.36510838313431</v>
+        <v>2.341218399466287</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0852273970587913</v>
-      </c>
-      <c r="C101">
-        <v>-18.99422456744514</v>
-      </c>
-      <c r="D101">
-        <v>182.8717754325549</v>
-      </c>
-      <c r="E101">
-        <v>28.74600000000001</v>
-      </c>
-      <c r="F101">
-        <v>203.346</v>
-      </c>
-      <c r="G101">
-        <v>1.48</v>
-      </c>
-      <c r="H101">
-        <v>30.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>38.66666666666666</v>
-      </c>
-      <c r="K101">
-        <v>2.58</v>
-      </c>
-      <c r="L101">
-        <v>36.08666666666667</v>
-      </c>
-      <c r="M101">
-        <v>15.4136268</v>
-      </c>
-      <c r="N101">
-        <v>20.67303986666666</v>
-      </c>
-      <c r="O101">
-        <v>4.961529567999999</v>
-      </c>
-      <c r="P101">
-        <v>15.71151029866666</v>
-      </c>
-      <c r="Q101">
-        <v>18.29151029866667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.819547705879127</v>
-      </c>
-      <c r="T101">
-        <v>57.03117225291879</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.05760800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.341218399466287</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
